--- a/Reproduce6 - AnalysisBySystem/Data_Analysis/generatedData/EFA_Summary_Consolidated.xlsx
+++ b/Reproduce6 - AnalysisBySystem/Data_Analysis/generatedData/EFA_Summary_Consolidated.xlsx
@@ -161,22 +161,19 @@
     <t xml:space="preserve">Complexity</t>
   </si>
   <si>
-    <t xml:space="preserve">visFaithful</t>
+    <t xml:space="preserve">analysisConfigure</t>
   </si>
   <si>
-    <t xml:space="preserve">visSimpleUnderstand</t>
+    <t xml:space="preserve">sysEasyStart</t>
   </si>
   <si>
-    <t xml:space="preserve">visAppropriate</t>
+    <t xml:space="preserve">sysEnjoy</t>
   </si>
   <si>
     <t xml:space="preserve">sysRetrieveInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">visRemember</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trialError</t>
+    <t xml:space="preserve">sysSimpleUnderstand</t>
   </si>
   <si>
     <t xml:space="preserve">sysThinkDeep</t>
@@ -185,19 +182,22 @@
     <t xml:space="preserve">sysUseful</t>
   </si>
   <si>
-    <t xml:space="preserve">sysEnjoy</t>
+    <t xml:space="preserve">taskComplete</t>
   </si>
   <si>
-    <t xml:space="preserve">tasksCompleteTask</t>
+    <t xml:space="preserve">trialError</t>
   </si>
   <si>
-    <t xml:space="preserve">sysSimpleUnderstand</t>
+    <t xml:space="preserve">visAppropriate</t>
   </si>
   <si>
-    <t xml:space="preserve">sysEasyStart</t>
+    <t xml:space="preserve">visFaithful</t>
   </si>
   <si>
-    <t xml:space="preserve">analysisConfigure</t>
+    <t xml:space="preserve">visRemember</t>
+  </si>
+  <si>
+    <t xml:space="preserve">visSimpleUnderstand</t>
   </si>
   <si>
     <t xml:space="preserve">Loading_F2</t>
@@ -596,25 +596,25 @@
         <v>5.41</v>
       </c>
       <c r="G2" t="n">
-        <v>0.744</v>
+        <v>0.752</v>
       </c>
       <c r="H2" t="n">
         <v>0.888</v>
       </c>
       <c r="I2" t="n">
-        <v>0.368</v>
+        <v>0.365</v>
       </c>
       <c r="J2" t="n">
         <v>0.533</v>
       </c>
       <c r="K2" t="n">
-        <v>0.279</v>
+        <v>0.28</v>
       </c>
       <c r="L2" t="n">
         <v>0.283</v>
       </c>
       <c r="M2" t="n">
-        <v>0.207</v>
+        <v>0.202</v>
       </c>
     </row>
     <row r="3">
@@ -637,25 +637,25 @@
         <v>4.609</v>
       </c>
       <c r="G3" t="n">
-        <v>1.24</v>
+        <v>1.247</v>
       </c>
       <c r="H3" t="n">
         <v>1.194</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8</v>
+        <v>0.794</v>
       </c>
       <c r="J3" t="n">
         <v>0.721</v>
       </c>
       <c r="K3" t="n">
-        <v>0.594</v>
+        <v>0.583</v>
       </c>
       <c r="L3" t="n">
         <v>0.46</v>
       </c>
       <c r="M3" t="n">
-        <v>0.418</v>
+        <v>0.406</v>
       </c>
     </row>
     <row r="4">
@@ -678,25 +678,25 @@
         <v>6.006</v>
       </c>
       <c r="G4" t="n">
-        <v>1.37</v>
+        <v>1.289</v>
       </c>
       <c r="H4" t="n">
         <v>1.267</v>
       </c>
       <c r="I4" t="n">
-        <v>0.836</v>
+        <v>0.834</v>
       </c>
       <c r="J4" t="n">
         <v>0.808</v>
       </c>
       <c r="K4" t="n">
-        <v>0.622</v>
+        <v>0.624</v>
       </c>
       <c r="L4" t="n">
         <v>0.334</v>
       </c>
       <c r="M4" t="n">
-        <v>0.428</v>
+        <v>0.439</v>
       </c>
     </row>
     <row r="5">
@@ -719,25 +719,25 @@
         <v>5.935</v>
       </c>
       <c r="G5" t="n">
-        <v>1.466</v>
+        <v>1.484</v>
       </c>
       <c r="H5" t="n">
         <v>0.785</v>
       </c>
       <c r="I5" t="n">
-        <v>0.918</v>
+        <v>0.921</v>
       </c>
       <c r="J5" t="n">
         <v>0.73</v>
       </c>
       <c r="K5" t="n">
-        <v>0.661</v>
+        <v>0.69</v>
       </c>
       <c r="L5" t="n">
         <v>0.418</v>
       </c>
       <c r="M5" t="n">
-        <v>0.474</v>
+        <v>0.486</v>
       </c>
     </row>
     <row r="6">
@@ -760,25 +760,25 @@
         <v>6.396</v>
       </c>
       <c r="G6" t="n">
-        <v>1.281</v>
+        <v>1.265</v>
       </c>
       <c r="H6" t="n">
         <v>1.442</v>
       </c>
       <c r="I6" t="n">
-        <v>0.801</v>
+        <v>0.813</v>
       </c>
       <c r="J6" t="n">
         <v>0.363</v>
       </c>
       <c r="K6" t="n">
-        <v>0.604</v>
+        <v>0.596</v>
       </c>
       <c r="L6" t="n">
         <v>0.346</v>
       </c>
       <c r="M6" t="n">
-        <v>0.428</v>
+        <v>0.424</v>
       </c>
     </row>
     <row r="7">
@@ -792,7 +792,7 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -801,25 +801,25 @@
         <v>6.087</v>
       </c>
       <c r="G7" t="n">
-        <v>1.286</v>
+        <v>1.294</v>
       </c>
       <c r="H7" t="n">
         <v>1.02</v>
       </c>
       <c r="I7" t="n">
-        <v>0.811</v>
+        <v>0.813</v>
       </c>
       <c r="J7" t="n">
         <v>0.806</v>
       </c>
       <c r="K7" t="n">
-        <v>0.589</v>
+        <v>0.603</v>
       </c>
       <c r="L7" t="n">
         <v>0.308</v>
       </c>
       <c r="M7" t="n">
-        <v>0.426</v>
+        <v>0.429</v>
       </c>
     </row>
   </sheetData>
@@ -864,25 +864,25 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0542</v>
+        <v>0.9782</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2507</v>
+        <v>0.1227</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7619</v>
+        <v>-0.2686</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0806</v>
+        <v>0.0632</v>
       </c>
       <c r="F2" t="n">
-        <v>0.503</v>
+        <v>0.8551</v>
       </c>
       <c r="G2" t="n">
-        <v>0.497</v>
+        <v>0.1449</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2497</v>
+        <v>1.1925</v>
       </c>
     </row>
     <row r="3">
@@ -890,25 +890,25 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5228</v>
+        <v>0.9328</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3466</v>
+        <v>-0.1715</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0777</v>
+        <v>-0.0078</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2078</v>
+        <v>0.1443</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5839</v>
+        <v>0.7467</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4161</v>
+        <v>0.2533</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1524</v>
+        <v>1.117</v>
       </c>
     </row>
     <row r="4">
@@ -916,25 +916,25 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.0657</v>
+        <v>0.298</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1145</v>
+        <v>0.7193</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7142</v>
+        <v>-0.1424</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0099</v>
+        <v>0.044</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5486</v>
+        <v>0.6755</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4514</v>
+        <v>0.3245</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0692</v>
+        <v>1.4307</v>
       </c>
     </row>
     <row r="5">
@@ -968,25 +968,25 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.4503</v>
+        <v>0.9529</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0737</v>
+        <v>-0.1546</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2271</v>
+        <v>0.1583</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4163</v>
+        <v>0.1069</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5526</v>
+        <v>0.9387</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4474</v>
+        <v>0.0613</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5402</v>
+        <v>1.1356</v>
       </c>
     </row>
     <row r="7">
@@ -994,25 +994,25 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.304</v>
+        <v>-0.2224</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2524</v>
+        <v>0.9639</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0897</v>
+        <v>-0.074</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5952</v>
+        <v>0.3514</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5285</v>
+        <v>0.8001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4715</v>
+        <v>0.1999</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9453</v>
+        <v>1.3924</v>
       </c>
     </row>
     <row r="8">
@@ -1020,25 +1020,25 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.2224</v>
+        <v>-0.1558</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9639</v>
+        <v>0.4984</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.074</v>
+        <v>0.4338</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3514</v>
+        <v>-0.0551</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8001</v>
+        <v>0.5306</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1999</v>
+        <v>0.4694</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3924</v>
+        <v>2.2023</v>
       </c>
     </row>
     <row r="9">
@@ -1046,25 +1046,25 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.1558</v>
+        <v>0.5118</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4984</v>
+        <v>0.0451</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4338</v>
+        <v>0.1522</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0551</v>
+        <v>0.2633</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5306</v>
+        <v>0.4104</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4694</v>
+        <v>0.5896</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2023</v>
+        <v>1.7181</v>
       </c>
     </row>
     <row r="10">
@@ -1072,25 +1072,25 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.298</v>
+        <v>0.304</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7193</v>
+        <v>0.2524</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1424</v>
+        <v>0.0897</v>
       </c>
       <c r="E10" t="n">
-        <v>0.044</v>
+        <v>0.5952</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6755</v>
+        <v>0.5285</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3245</v>
+        <v>0.4715</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4307</v>
+        <v>1.9453</v>
       </c>
     </row>
     <row r="11">
@@ -1098,25 +1098,25 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5118</v>
+        <v>-0.0657</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0451</v>
+        <v>0.1145</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1522</v>
+        <v>0.7142</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2633</v>
+        <v>-0.0099</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4104</v>
+        <v>0.5486</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5896</v>
+        <v>0.4514</v>
       </c>
       <c r="H11" t="n">
-        <v>1.7181</v>
+        <v>1.0692</v>
       </c>
     </row>
     <row r="12">
@@ -1124,25 +1124,25 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.9529</v>
+        <v>0.0542</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1546</v>
+        <v>-0.2507</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1583</v>
+        <v>0.7619</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1069</v>
+        <v>0.0806</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9387</v>
+        <v>0.503</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0613</v>
+        <v>0.497</v>
       </c>
       <c r="H12" t="n">
-        <v>1.1356</v>
+        <v>1.2497</v>
       </c>
     </row>
     <row r="13">
@@ -1150,25 +1150,25 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.9328</v>
+        <v>0.4503</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.1715</v>
+        <v>-0.0737</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0078</v>
+        <v>0.2271</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1443</v>
+        <v>-0.4163</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7467</v>
+        <v>0.5526</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2533</v>
+        <v>0.4474</v>
       </c>
       <c r="H13" t="n">
-        <v>1.117</v>
+        <v>2.5402</v>
       </c>
     </row>
     <row r="14">
@@ -1176,25 +1176,25 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.9782</v>
+        <v>0.5228</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1227</v>
+        <v>0.3466</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2686</v>
+        <v>-0.0777</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0632</v>
+        <v>-0.2078</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8551</v>
+        <v>0.5839</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1449</v>
+        <v>0.4161</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1925</v>
+        <v>2.1524</v>
       </c>
     </row>
   </sheetData>
@@ -1230,13 +1230,13 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5412</v>
+        <v>0.7516</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2928</v>
+        <v>0.5649</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7072</v>
+        <v>0.4351</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -1247,13 +1247,13 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7192</v>
+        <v>0.7155</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5172</v>
+        <v>0.512</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4828</v>
+        <v>0.488</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -1264,13 +1264,13 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5393</v>
+        <v>0.7587</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2909</v>
+        <v>0.5756</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7091</v>
+        <v>0.4244</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -1298,13 +1298,13 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7187</v>
+        <v>0.6911</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5166</v>
+        <v>0.4777</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4834</v>
+        <v>0.5223</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -1315,13 +1315,13 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7038</v>
+        <v>0.6728</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4954</v>
+        <v>0.4527</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5046</v>
+        <v>0.5473</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -1332,13 +1332,13 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.6728</v>
+        <v>0.4992</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4527</v>
+        <v>0.2492</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5473</v>
+        <v>0.7508</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -1349,13 +1349,13 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4992</v>
+        <v>0.684</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2492</v>
+        <v>0.4679</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7508</v>
+        <v>0.5321</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -1366,13 +1366,13 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7587</v>
+        <v>0.7038</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5756</v>
+        <v>0.4954</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4244</v>
+        <v>0.5046</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -1383,13 +1383,13 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.684</v>
+        <v>0.5393</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4679</v>
+        <v>0.2909</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5321</v>
+        <v>0.7091</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -1400,13 +1400,13 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.6911</v>
+        <v>0.5412</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4777</v>
+        <v>0.2928</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5223</v>
+        <v>0.7072</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -1417,13 +1417,13 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.7155</v>
+        <v>0.7187</v>
       </c>
       <c r="C13" t="n">
-        <v>0.512</v>
+        <v>0.5166</v>
       </c>
       <c r="D13" t="n">
-        <v>0.488</v>
+        <v>0.4834</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -1434,13 +1434,13 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.7516</v>
+        <v>0.7192</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5649</v>
+        <v>0.5172</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4351</v>
+        <v>0.4828</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -1482,19 +1482,19 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0093</v>
+        <v>0.7094</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6526</v>
+        <v>0.0822</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4337</v>
+        <v>0.5841</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5663</v>
+        <v>0.4159</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0004</v>
+        <v>1.0269</v>
       </c>
     </row>
     <row r="3">
@@ -1502,19 +1502,19 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3565</v>
+        <v>0.8531</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4601</v>
+        <v>-0.132</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5471</v>
+        <v>0.6021</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4529</v>
+        <v>0.3979</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8825</v>
+        <v>1.0479</v>
       </c>
     </row>
     <row r="4">
@@ -1522,19 +1522,19 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.203</v>
+        <v>0.7468</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9016</v>
+        <v>0.0467</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6217</v>
+        <v>0.6042</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3783</v>
+        <v>0.3958</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1011</v>
+        <v>1.0078</v>
       </c>
     </row>
     <row r="5">
@@ -1562,19 +1562,19 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.6238</v>
+        <v>0.6447</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1432</v>
+        <v>0.0847</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5231</v>
+        <v>0.4921</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4769</v>
+        <v>0.5079</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1051</v>
+        <v>1.0345</v>
       </c>
     </row>
     <row r="7">
@@ -1582,19 +1582,19 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.627</v>
+        <v>0.9028</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1212</v>
+        <v>-0.2432</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5043</v>
+        <v>0.5953</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4957</v>
+        <v>0.4047</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0746</v>
+        <v>1.1444</v>
       </c>
     </row>
     <row r="8">
@@ -1602,19 +1602,19 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.9028</v>
+        <v>-0.0423</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2432</v>
+        <v>0.6623</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5953</v>
+        <v>0.4048</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4047</v>
+        <v>0.5952</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1444</v>
+        <v>1.0082</v>
       </c>
     </row>
     <row r="9">
@@ -1622,19 +1622,19 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0423</v>
+        <v>0.2901</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6623</v>
+        <v>0.4956</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4048</v>
+        <v>0.5123</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5952</v>
+        <v>0.4877</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0082</v>
+        <v>1.6132</v>
       </c>
     </row>
     <row r="10">
@@ -1642,19 +1642,19 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7468</v>
+        <v>0.627</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0467</v>
+        <v>0.1212</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6042</v>
+        <v>0.5043</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3958</v>
+        <v>0.4957</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0078</v>
+        <v>1.0746</v>
       </c>
     </row>
     <row r="11">
@@ -1662,19 +1662,19 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2901</v>
+        <v>-0.203</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4956</v>
+        <v>0.9016</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5123</v>
+        <v>0.6217</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4877</v>
+        <v>0.3783</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6132</v>
+        <v>1.1011</v>
       </c>
     </row>
     <row r="12">
@@ -1682,19 +1682,19 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.6447</v>
+        <v>0.0093</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0847</v>
+        <v>0.6526</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4921</v>
+        <v>0.4337</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5079</v>
+        <v>0.5663</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0345</v>
+        <v>1.0004</v>
       </c>
     </row>
     <row r="13">
@@ -1702,19 +1702,19 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.8531</v>
+        <v>0.6238</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.132</v>
+        <v>0.1432</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6021</v>
+        <v>0.5231</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3979</v>
+        <v>0.4769</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0479</v>
+        <v>1.1051</v>
       </c>
     </row>
     <row r="14">
@@ -1722,19 +1722,19 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.7094</v>
+        <v>0.3565</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0822</v>
+        <v>0.4601</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5841</v>
+        <v>0.5471</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4159</v>
+        <v>0.4529</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0269</v>
+        <v>1.8825</v>
       </c>
     </row>
   </sheetData>
@@ -1776,22 +1776,22 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1524</v>
+        <v>0.7232</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6508</v>
+        <v>0.0278</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3146</v>
+        <v>0.0583</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5181</v>
+        <v>0.5952</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4819</v>
+        <v>0.4048</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5699</v>
+        <v>1.016</v>
       </c>
     </row>
     <row r="3">
@@ -1799,22 +1799,22 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5214</v>
+        <v>0.9136</v>
       </c>
       <c r="C3" t="n">
-        <v>0.375</v>
+        <v>-0.1941</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0956</v>
+        <v>-0.0245</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5717</v>
+        <v>0.6484</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4283</v>
+        <v>0.3516</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8958</v>
+        <v>1.0916</v>
       </c>
     </row>
     <row r="4">
@@ -1822,22 +1822,22 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.0513</v>
+        <v>0.6396</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8316</v>
+        <v>0.0182</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0515</v>
+        <v>0.2062</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6219</v>
+        <v>0.6045</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3781</v>
+        <v>0.3955</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0153</v>
+        <v>1.2074</v>
       </c>
     </row>
     <row r="5">
@@ -1868,22 +1868,22 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.4951</v>
+        <v>0.7719</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1221</v>
+        <v>0.0097</v>
       </c>
       <c r="D6" t="n">
-        <v>0.239</v>
+        <v>-0.0882</v>
       </c>
       <c r="E6" t="n">
-        <v>0.529</v>
+        <v>0.5412</v>
       </c>
       <c r="F6" t="n">
-        <v>0.471</v>
+        <v>0.4588</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5823</v>
+        <v>1.0265</v>
       </c>
     </row>
     <row r="7">
@@ -1891,22 +1891,22 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4977</v>
+        <v>0.5895</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1012</v>
+        <v>-0.2209</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2362</v>
+        <v>0.4266</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5096</v>
+        <v>0.6258</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4904</v>
+        <v>0.3742</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5243</v>
+        <v>2.1402</v>
       </c>
     </row>
     <row r="8">
@@ -1914,22 +1914,22 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.5895</v>
+        <v>0.0111</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2209</v>
+        <v>0.6165</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4266</v>
+        <v>0.0437</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6258</v>
+        <v>0.4084</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3742</v>
+        <v>0.5916</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1402</v>
+        <v>1.0107</v>
       </c>
     </row>
     <row r="9">
@@ -1937,22 +1937,22 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0111</v>
+        <v>0.606</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6165</v>
+        <v>0.38</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0437</v>
+        <v>-0.2833</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4084</v>
+        <v>0.6078</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5916</v>
+        <v>0.3922</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0107</v>
+        <v>2.1607</v>
       </c>
     </row>
     <row r="10">
@@ -1960,22 +1960,22 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.6396</v>
+        <v>0.4977</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0182</v>
+        <v>0.1012</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2062</v>
+        <v>0.2362</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6045</v>
+        <v>0.5096</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3955</v>
+        <v>0.4904</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2074</v>
+        <v>1.5243</v>
       </c>
     </row>
     <row r="11">
@@ -1983,22 +1983,22 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.606</v>
+        <v>-0.0513</v>
       </c>
       <c r="C11" t="n">
-        <v>0.38</v>
+        <v>0.8316</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2833</v>
+        <v>-0.0515</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6078</v>
+        <v>0.6219</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3922</v>
+        <v>0.3781</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1607</v>
+        <v>1.0153</v>
       </c>
     </row>
     <row r="12">
@@ -2006,22 +2006,22 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.7719</v>
+        <v>-0.1524</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0097</v>
+        <v>0.6508</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0882</v>
+        <v>0.3146</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5412</v>
+        <v>0.5181</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4588</v>
+        <v>0.4819</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0265</v>
+        <v>1.5699</v>
       </c>
     </row>
     <row r="13">
@@ -2029,22 +2029,22 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.9136</v>
+        <v>0.4951</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.1941</v>
+        <v>0.1221</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0245</v>
+        <v>0.239</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6484</v>
+        <v>0.529</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3516</v>
+        <v>0.471</v>
       </c>
       <c r="G13" t="n">
-        <v>1.0916</v>
+        <v>1.5823</v>
       </c>
     </row>
     <row r="14">
@@ -2052,22 +2052,22 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.7232</v>
+        <v>0.5214</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0278</v>
+        <v>0.375</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0583</v>
+        <v>-0.0956</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5952</v>
+        <v>0.5717</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4048</v>
+        <v>0.4283</v>
       </c>
       <c r="G14" t="n">
-        <v>1.016</v>
+        <v>1.8958</v>
       </c>
     </row>
   </sheetData>
@@ -2103,13 +2103,13 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7479</v>
+        <v>0.5955</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5593</v>
+        <v>0.3546</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4407</v>
+        <v>0.6454</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -2120,13 +2120,13 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6947</v>
+        <v>0.7151</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4826</v>
+        <v>0.5113</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5174</v>
+        <v>0.4887</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -2137,13 +2137,13 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6566</v>
+        <v>0.5671</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4312</v>
+        <v>0.3216</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5688</v>
+        <v>0.6784</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -2171,13 +2171,13 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.6312</v>
+        <v>0.7386</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3985</v>
+        <v>0.5456</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6015</v>
+        <v>0.4544</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -2188,13 +2188,13 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4939</v>
+        <v>0.4631</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2439</v>
+        <v>0.2145</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7561</v>
+        <v>0.7855</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -2205,13 +2205,13 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.4631</v>
+        <v>0.8109</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2145</v>
+        <v>0.6575</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7855</v>
+        <v>0.3425</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -2222,13 +2222,13 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.8109</v>
+        <v>0.6732</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6575</v>
+        <v>0.4532</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3425</v>
+        <v>0.5468</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -2239,13 +2239,13 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5671</v>
+        <v>0.4939</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3216</v>
+        <v>0.2439</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6784</v>
+        <v>0.7561</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -2256,13 +2256,13 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6732</v>
+        <v>0.6566</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4532</v>
+        <v>0.4312</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5468</v>
+        <v>0.5688</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -2273,13 +2273,13 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.7386</v>
+        <v>0.7479</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5456</v>
+        <v>0.5593</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4544</v>
+        <v>0.4407</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -2290,13 +2290,13 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.7151</v>
+        <v>0.6312</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5113</v>
+        <v>0.3985</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4887</v>
+        <v>0.6015</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -2307,13 +2307,13 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.5955</v>
+        <v>0.6947</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3546</v>
+        <v>0.4826</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6454</v>
+        <v>0.5174</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -2355,19 +2355,19 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6545</v>
+        <v>0.4165</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1271</v>
+        <v>0.2127</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5724</v>
+        <v>0.3549</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4276</v>
+        <v>0.6451</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0753</v>
+        <v>1.4883</v>
       </c>
     </row>
     <row r="3">
@@ -2375,19 +2375,19 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2704</v>
+        <v>0.2219</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4778</v>
+        <v>0.5519</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5</v>
+        <v>0.5421</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5</v>
+        <v>0.4579</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5808</v>
+        <v>1.3149</v>
       </c>
     </row>
     <row r="4">
@@ -2395,19 +2395,19 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
+        <v>0.1725</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.4413</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.6584</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.0223</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.4566</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.5434</v>
-      </c>
       <c r="F4" t="n">
-        <v>1.0023</v>
+        <v>1.2987</v>
       </c>
     </row>
     <row r="5">
@@ -2435,19 +2435,19 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.581</v>
+        <v>0.1609</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0768</v>
+        <v>0.6428</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4121</v>
+        <v>0.5981</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5879</v>
+        <v>0.4019</v>
       </c>
       <c r="F6" t="n">
-        <v>1.035</v>
+        <v>1.1249</v>
       </c>
     </row>
     <row r="7">
@@ -2455,19 +2455,19 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.1848</v>
+        <v>0.0345</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7414</v>
+        <v>0.4739</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3732</v>
+        <v>0.2509</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6268</v>
+        <v>0.7491</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1238</v>
+        <v>1.0106</v>
       </c>
     </row>
     <row r="8">
@@ -2475,19 +2475,19 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0345</v>
+        <v>1.0523</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4739</v>
+        <v>-0.2273</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2509</v>
+        <v>0.7913</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7491</v>
+        <v>0.2087</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0106</v>
+        <v>1.0931</v>
       </c>
     </row>
     <row r="9">
@@ -2495,19 +2495,19 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>1.0523</v>
+        <v>0.6481</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.2273</v>
+        <v>0.0516</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7913</v>
+        <v>0.4741</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2087</v>
+        <v>0.5259</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0931</v>
+        <v>1.0127</v>
       </c>
     </row>
     <row r="10">
@@ -2515,19 +2515,19 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1725</v>
+        <v>-0.1848</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4413</v>
+        <v>0.7414</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3416</v>
+        <v>0.3732</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6584</v>
+        <v>0.6268</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2987</v>
+        <v>1.1238</v>
       </c>
     </row>
     <row r="11">
@@ -2535,19 +2535,19 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6481</v>
+        <v>0.6584</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0516</v>
+        <v>0.0223</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4741</v>
+        <v>0.4566</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5259</v>
+        <v>0.5434</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0127</v>
+        <v>1.0023</v>
       </c>
     </row>
     <row r="12">
@@ -2555,19 +2555,19 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1609</v>
+        <v>0.6545</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6428</v>
+        <v>0.1271</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5981</v>
+        <v>0.5724</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4019</v>
+        <v>0.4276</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1249</v>
+        <v>1.0753</v>
       </c>
     </row>
     <row r="13">
@@ -2575,19 +2575,19 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2219</v>
+        <v>0.581</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5519</v>
+        <v>0.0768</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5421</v>
+        <v>0.4121</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4579</v>
+        <v>0.5879</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3149</v>
+        <v>1.035</v>
       </c>
     </row>
     <row r="14">
@@ -2595,19 +2595,19 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.4165</v>
+        <v>0.2704</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2127</v>
+        <v>0.4778</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3549</v>
+        <v>0.5</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6451</v>
+        <v>0.5</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4883</v>
+        <v>1.5808</v>
       </c>
     </row>
   </sheetData>
@@ -2649,22 +2649,22 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4834</v>
+        <v>0.2659</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3083</v>
+        <v>0.3913</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0491</v>
+        <v>0.011</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5771</v>
+        <v>0.3727</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4229</v>
+        <v>0.6273</v>
       </c>
       <c r="G2" t="n">
-        <v>1.723</v>
+        <v>1.7631</v>
       </c>
     </row>
     <row r="3">
@@ -2672,22 +2672,22 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0893</v>
+        <v>0.1297</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6589</v>
+        <v>0.3444</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0379</v>
+        <v>0.3729</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5569</v>
+        <v>0.5443</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4431</v>
+        <v>0.4557</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0435</v>
+        <v>2.2364</v>
       </c>
     </row>
     <row r="4">
@@ -2695,22 +2695,22 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5325</v>
+        <v>0.1744</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1019</v>
+        <v>-0.0273</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1096</v>
+        <v>0.553</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4587</v>
+        <v>0.4215</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5413</v>
+        <v>0.5785</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1606</v>
+        <v>1.2023</v>
       </c>
     </row>
     <row r="5">
@@ -2741,22 +2741,22 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.3606</v>
+        <v>0.0758</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5434</v>
+        <v>0.3723</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2242</v>
+        <v>0.4333</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5013</v>
+        <v>0.6019</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4987</v>
+        <v>0.3981</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1212</v>
+        <v>2.0238</v>
       </c>
     </row>
     <row r="7">
@@ -2764,22 +2764,22 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.2641</v>
+        <v>0.058</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5846</v>
+        <v>-0.022</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2721</v>
+        <v>0.5483</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3879</v>
+        <v>0.3243</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6121</v>
+        <v>0.6757</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8543</v>
+        <v>1.0256</v>
       </c>
     </row>
     <row r="8">
@@ -2787,22 +2787,22 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.058</v>
+        <v>0.9158</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.022</v>
+        <v>-0.1518</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5483</v>
+        <v>0.1524</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3243</v>
+        <v>0.8277</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6757</v>
+        <v>0.1723</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0256</v>
+        <v>1.1116</v>
       </c>
     </row>
     <row r="9">
@@ -2810,22 +2810,22 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.9158</v>
+        <v>0.5629</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.1518</v>
+        <v>-0.0506</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1524</v>
+        <v>0.2681</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8277</v>
+        <v>0.5074</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1723</v>
+        <v>0.4926</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1116</v>
+        <v>1.4503</v>
       </c>
     </row>
     <row r="10">
@@ -2833,22 +2833,22 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1744</v>
+        <v>-0.2641</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0273</v>
+        <v>0.5846</v>
       </c>
       <c r="D10" t="n">
-        <v>0.553</v>
+        <v>0.2721</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4215</v>
+        <v>0.3879</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5785</v>
+        <v>0.6121</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2023</v>
+        <v>1.8543</v>
       </c>
     </row>
     <row r="11">
@@ -2856,22 +2856,22 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5629</v>
+        <v>0.5325</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0506</v>
+        <v>0.1019</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2681</v>
+        <v>0.1096</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5074</v>
+        <v>0.4587</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4926</v>
+        <v>0.5413</v>
       </c>
       <c r="G11" t="n">
-        <v>1.4503</v>
+        <v>1.1606</v>
       </c>
     </row>
     <row r="12">
@@ -2879,22 +2879,22 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0758</v>
+        <v>0.4834</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3723</v>
+        <v>0.3083</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4333</v>
+        <v>0.0491</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6019</v>
+        <v>0.5771</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3981</v>
+        <v>0.4229</v>
       </c>
       <c r="G12" t="n">
-        <v>2.0238</v>
+        <v>1.723</v>
       </c>
     </row>
     <row r="13">
@@ -2902,22 +2902,22 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1297</v>
+        <v>0.3606</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3444</v>
+        <v>0.5434</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3729</v>
+        <v>-0.2242</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5443</v>
+        <v>0.5013</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4557</v>
+        <v>0.4987</v>
       </c>
       <c r="G13" t="n">
-        <v>2.2364</v>
+        <v>2.1212</v>
       </c>
     </row>
     <row r="14">
@@ -2925,22 +2925,22 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.2659</v>
+        <v>0.0893</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3913</v>
+        <v>0.6589</v>
       </c>
       <c r="D14" t="n">
-        <v>0.011</v>
+        <v>0.0379</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3727</v>
+        <v>0.5569</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6273</v>
+        <v>0.4431</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7631</v>
+        <v>1.0435</v>
       </c>
     </row>
   </sheetData>
@@ -2985,25 +2985,25 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4999</v>
+        <v>0.2061</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0616</v>
+        <v>0.0014</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0382</v>
+        <v>-0.0455</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2382</v>
+        <v>0.5073</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5806</v>
+        <v>0.4088</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4194</v>
+        <v>0.5912</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4811</v>
+        <v>1.3396</v>
       </c>
     </row>
     <row r="3">
@@ -3011,25 +3011,25 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2779</v>
+        <v>0.0687</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0011</v>
+        <v>0.3475</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5507</v>
+        <v>0.1176</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0031</v>
+        <v>0.3317</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5667</v>
+        <v>0.5542</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4333</v>
+        <v>0.4458</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4783</v>
+        <v>2.311</v>
       </c>
     </row>
     <row r="4">
@@ -3037,25 +3037,25 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5721</v>
+        <v>0.0928</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1395</v>
+        <v>0.5528</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0314</v>
+        <v>0.0287</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0084</v>
+        <v>0.0312</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4602</v>
+        <v>0.4216</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5398</v>
+        <v>0.5784</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1252</v>
+        <v>1.0685</v>
       </c>
     </row>
     <row r="5">
@@ -3089,25 +3089,25 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5128</v>
+        <v>0.0068</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.2288</v>
+        <v>0.4003</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2783</v>
+        <v>0.1483</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1322</v>
+        <v>0.3496</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5016</v>
+        <v>0.6126</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4984</v>
+        <v>0.3874</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1522</v>
+        <v>2.2561</v>
       </c>
     </row>
     <row r="7">
@@ -3115,25 +3115,25 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.0963</v>
+        <v>0.0008</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2061</v>
+        <v>0.5396</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6646</v>
+        <v>0.0999</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.119</v>
+        <v>-0.0434</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4098</v>
+        <v>0.3258</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5902</v>
+        <v>0.6742</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3068</v>
+        <v>1.0818</v>
       </c>
     </row>
     <row r="8">
@@ -3141,25 +3141,25 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0008</v>
+        <v>0.9332</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5396</v>
+        <v>0.2274</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0999</v>
+        <v>-0.1565</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0434</v>
+        <v>-0.1245</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3258</v>
+        <v>0.833</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6742</v>
+        <v>0.167</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0818</v>
+        <v>1.2161</v>
       </c>
     </row>
     <row r="9">
@@ -3167,25 +3167,25 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.9332</v>
+        <v>0.55</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2274</v>
+        <v>0.3064</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1565</v>
+        <v>-0.0549</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1245</v>
+        <v>-0.0374</v>
       </c>
       <c r="F9" t="n">
-        <v>0.833</v>
+        <v>0.5088</v>
       </c>
       <c r="G9" t="n">
-        <v>0.167</v>
+        <v>0.4912</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2161</v>
+        <v>1.6011</v>
       </c>
     </row>
     <row r="10">
@@ -3193,25 +3193,25 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0928</v>
+        <v>-0.0963</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5528</v>
+        <v>0.2061</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0287</v>
+        <v>0.6646</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0312</v>
+        <v>-0.119</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4216</v>
+        <v>0.4098</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5784</v>
+        <v>0.5902</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0685</v>
+        <v>1.3068</v>
       </c>
     </row>
     <row r="11">
@@ -3219,25 +3219,25 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.55</v>
+        <v>0.5721</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3064</v>
+        <v>0.1395</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0549</v>
+        <v>0.0314</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0374</v>
+        <v>-0.0084</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5088</v>
+        <v>0.4602</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4912</v>
+        <v>0.5398</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6011</v>
+        <v>1.1252</v>
       </c>
     </row>
     <row r="12">
@@ -3245,25 +3245,25 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0068</v>
+        <v>0.4999</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4003</v>
+        <v>0.0616</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1483</v>
+        <v>0.0382</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3496</v>
+        <v>0.2382</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6126</v>
+        <v>0.5806</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3874</v>
+        <v>0.4194</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2561</v>
+        <v>1.4811</v>
       </c>
     </row>
     <row r="13">
@@ -3271,25 +3271,25 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0687</v>
+        <v>0.5128</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3475</v>
+        <v>-0.2288</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1176</v>
+        <v>0.2783</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3317</v>
+        <v>0.1322</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5542</v>
+        <v>0.5016</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4458</v>
+        <v>0.4984</v>
       </c>
       <c r="H13" t="n">
-        <v>2.311</v>
+        <v>2.1522</v>
       </c>
     </row>
     <row r="14">
@@ -3297,25 +3297,25 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.2061</v>
+        <v>0.2779</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0014</v>
+        <v>-0.0011</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0455</v>
+        <v>0.5507</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5073</v>
+        <v>0.0031</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4088</v>
+        <v>0.5667</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5912</v>
+        <v>0.4333</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3396</v>
+        <v>1.4783</v>
       </c>
     </row>
   </sheetData>
@@ -3351,13 +3351,13 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4721</v>
+        <v>0.6298</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2229</v>
+        <v>0.3966</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7771</v>
+        <v>0.6034</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3368,13 +3368,13 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.691</v>
+        <v>0.7</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4774</v>
+        <v>0.49</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5226</v>
+        <v>0.51</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3385,13 +3385,13 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6969</v>
+        <v>0.7178</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4857</v>
+        <v>0.5152</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5143</v>
+        <v>0.4848</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -3419,13 +3419,13 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.6487</v>
+        <v>0.7592</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4208</v>
+        <v>0.5764</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5792</v>
+        <v>0.4236</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -3436,13 +3436,13 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7691</v>
+        <v>0.7178</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5915</v>
+        <v>0.5152</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4085</v>
+        <v>0.4848</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -3453,13 +3453,13 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7178</v>
+        <v>0.7262</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5152</v>
+        <v>0.5273</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4848</v>
+        <v>0.4727</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -3470,13 +3470,13 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.7262</v>
+        <v>0.6763</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5273</v>
+        <v>0.4573</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4727</v>
+        <v>0.5427</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -3487,13 +3487,13 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7178</v>
+        <v>0.7691</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5152</v>
+        <v>0.5915</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4848</v>
+        <v>0.4085</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -3504,13 +3504,13 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6763</v>
+        <v>0.6969</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4573</v>
+        <v>0.4857</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5427</v>
+        <v>0.5143</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -3521,13 +3521,13 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.7592</v>
+        <v>0.4721</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5764</v>
+        <v>0.2229</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4236</v>
+        <v>0.7771</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -3538,13 +3538,13 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.7</v>
+        <v>0.6487</v>
       </c>
       <c r="C13" t="n">
-        <v>0.49</v>
+        <v>0.4208</v>
       </c>
       <c r="D13" t="n">
-        <v>0.51</v>
+        <v>0.5792</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -3555,13 +3555,13 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6298</v>
+        <v>0.691</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3966</v>
+        <v>0.4774</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6034</v>
+        <v>0.5226</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -3603,19 +3603,19 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.3351</v>
+        <v>0.8622</v>
       </c>
       <c r="C2" t="n">
-        <v>0.88</v>
+        <v>-0.1807</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5185</v>
+        <v>0.5815</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4815</v>
+        <v>0.4185</v>
       </c>
       <c r="F2" t="n">
-        <v>1.284</v>
+        <v>1.0877</v>
       </c>
     </row>
     <row r="3">
@@ -3623,19 +3623,19 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4644</v>
+        <v>0.7946</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3</v>
+        <v>-0.0315</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4796</v>
+        <v>0.6012</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5204</v>
+        <v>0.3988</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7107</v>
+        <v>1.0031</v>
       </c>
     </row>
     <row r="4">
@@ -3643,19 +3643,19 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.0452</v>
+        <v>0.6524</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8341</v>
+        <v>0.1358</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6507</v>
+        <v>0.5546</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3493</v>
+        <v>0.4454</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0059</v>
+        <v>1.0865</v>
       </c>
     </row>
     <row r="5">
@@ -3683,19 +3683,19 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.6231</v>
+        <v>1.0563</v>
       </c>
       <c r="C6" t="n">
-        <v>0.088</v>
+        <v>-0.2354</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4644</v>
+        <v>0.8608</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5356</v>
+        <v>0.1392</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0399</v>
+        <v>1.0991</v>
       </c>
     </row>
     <row r="7">
@@ -3703,19 +3703,19 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4761</v>
+        <v>0.2036</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3761</v>
+        <v>0.6001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5918</v>
+        <v>0.5542</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4082</v>
+        <v>0.4458</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8982</v>
+        <v>1.2273</v>
       </c>
     </row>
     <row r="8">
@@ -3723,19 +3723,19 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2036</v>
+        <v>0.0256</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6001</v>
+        <v>0.7939</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5542</v>
+        <v>0.6562</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4458</v>
+        <v>0.3438</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2273</v>
+        <v>1.0021</v>
       </c>
     </row>
     <row r="9">
@@ -3743,19 +3743,19 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0256</v>
+        <v>0.1049</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7939</v>
+        <v>0.6553</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6562</v>
+        <v>0.5263</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3438</v>
+        <v>0.4737</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0021</v>
+        <v>1.0513</v>
       </c>
     </row>
     <row r="10">
@@ -3763,19 +3763,19 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.6524</v>
+        <v>0.4761</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1358</v>
+        <v>0.3761</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5546</v>
+        <v>0.5918</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4454</v>
+        <v>0.4082</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0865</v>
+        <v>1.8982</v>
       </c>
     </row>
     <row r="11">
@@ -3783,19 +3783,19 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1049</v>
+        <v>-0.0452</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6553</v>
+        <v>0.8341</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5263</v>
+        <v>0.6507</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4737</v>
+        <v>0.3493</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0513</v>
+        <v>1.0059</v>
       </c>
     </row>
     <row r="12">
@@ -3803,19 +3803,19 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>1.0563</v>
+        <v>-0.3351</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.2354</v>
+        <v>0.88</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8608</v>
+        <v>0.5185</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1392</v>
+        <v>0.4815</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0991</v>
+        <v>1.284</v>
       </c>
     </row>
     <row r="13">
@@ -3823,19 +3823,19 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.7946</v>
+        <v>0.6231</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.0315</v>
+        <v>0.088</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6012</v>
+        <v>0.4644</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3988</v>
+        <v>0.5356</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0031</v>
+        <v>1.0399</v>
       </c>
     </row>
     <row r="14">
@@ -3843,19 +3843,19 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.8622</v>
+        <v>0.4644</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.1807</v>
+        <v>0.3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5815</v>
+        <v>0.4796</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4185</v>
+        <v>0.5204</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0877</v>
+        <v>1.7107</v>
       </c>
     </row>
   </sheetData>
@@ -6136,22 +6136,22 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9021</v>
+        <v>-0.2596</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0991</v>
+        <v>0.4826</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2525</v>
+        <v>0.5109</v>
       </c>
       <c r="E2" t="n">
-        <v>0.554</v>
+        <v>0.6134</v>
       </c>
       <c r="F2" t="n">
-        <v>0.446</v>
+        <v>0.3866</v>
       </c>
       <c r="G2" t="n">
-        <v>1.1816</v>
+        <v>2.4826</v>
       </c>
     </row>
     <row r="3">
@@ -6159,22 +6159,22 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3179</v>
+        <v>-0.034</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4546</v>
+        <v>0.6271</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0287</v>
+        <v>0.218</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4921</v>
+        <v>0.6016</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5079</v>
+        <v>0.3984</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7989</v>
+        <v>1.2448</v>
       </c>
     </row>
     <row r="4">
@@ -6182,22 +6182,22 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7696</v>
+        <v>0.0074</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.0754</v>
+        <v>0.2408</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1221</v>
+        <v>0.5927</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6507</v>
+        <v>0.6159</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3493</v>
+        <v>0.3841</v>
       </c>
       <c r="G4" t="n">
-        <v>1.07</v>
+        <v>1.3216</v>
       </c>
     </row>
     <row r="5">
@@ -6228,22 +6228,22 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1265</v>
+        <v>-0.1028</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6015</v>
+        <v>1.126</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0218</v>
+        <v>-0.1531</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4811</v>
+        <v>0.9561</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5189</v>
+        <v>0.0439</v>
       </c>
       <c r="G6" t="n">
-        <v>1.091</v>
+        <v>1.0539</v>
       </c>
     </row>
     <row r="7">
@@ -6251,22 +6251,22 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2865</v>
+        <v>0.4657</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2224</v>
+        <v>-0.0709</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3902</v>
+        <v>0.4489</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6071</v>
+        <v>0.5941</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3929</v>
+        <v>0.4059</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4884</v>
+        <v>2.045</v>
       </c>
     </row>
     <row r="8">
@@ -6274,22 +6274,22 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.4657</v>
+        <v>0.733</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0709</v>
+        <v>-0.0156</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4489</v>
+        <v>0.1324</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5941</v>
+        <v>0.6563</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4059</v>
+        <v>0.3437</v>
       </c>
       <c r="G8" t="n">
-        <v>2.045</v>
+        <v>1.0661</v>
       </c>
     </row>
     <row r="9">
@@ -6297,22 +6297,22 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.733</v>
+        <v>0.6368</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.0156</v>
+        <v>0.1285</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1324</v>
+        <v>0.0231</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6563</v>
+        <v>0.5318</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3437</v>
+        <v>0.4682</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0661</v>
+        <v>1.0841</v>
       </c>
     </row>
     <row r="10">
@@ -6320,22 +6320,22 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0074</v>
+        <v>0.2865</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2408</v>
+        <v>0.2224</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5927</v>
+        <v>0.3902</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6159</v>
+        <v>0.6071</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3841</v>
+        <v>0.3929</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3216</v>
+        <v>2.4884</v>
       </c>
     </row>
     <row r="11">
@@ -6343,22 +6343,22 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6368</v>
+        <v>0.7696</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1285</v>
+        <v>-0.0754</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0231</v>
+        <v>0.1221</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5318</v>
+        <v>0.6507</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4682</v>
+        <v>0.3493</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0841</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="12">
@@ -6366,22 +6366,22 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.1028</v>
+        <v>0.9021</v>
       </c>
       <c r="C12" t="n">
-        <v>1.126</v>
+        <v>-0.0991</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1531</v>
+        <v>-0.2525</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9561</v>
+        <v>0.554</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0439</v>
+        <v>0.446</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0539</v>
+        <v>1.1816</v>
       </c>
     </row>
     <row r="13">
@@ -6389,22 +6389,22 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.034</v>
+        <v>0.1265</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6271</v>
+        <v>0.6015</v>
       </c>
       <c r="D13" t="n">
-        <v>0.218</v>
+        <v>0.0218</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6016</v>
+        <v>0.4811</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3984</v>
+        <v>0.5189</v>
       </c>
       <c r="G13" t="n">
-        <v>1.2448</v>
+        <v>1.091</v>
       </c>
     </row>
     <row r="14">
@@ -6412,22 +6412,22 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.2596</v>
+        <v>0.3179</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4826</v>
+        <v>0.4546</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5109</v>
+        <v>0.0287</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6134</v>
+        <v>0.4921</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3866</v>
+        <v>0.5079</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4826</v>
+        <v>1.7989</v>
       </c>
     </row>
   </sheetData>
@@ -6472,25 +6472,25 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9049</v>
+        <v>-0.1039</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1415</v>
+        <v>0.7835</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1511</v>
+        <v>0.288</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.049</v>
+        <v>-0.1853</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5702</v>
+        <v>0.6498</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4298</v>
+        <v>0.3502</v>
       </c>
       <c r="H2" t="n">
-        <v>1.112</v>
+        <v>1.4298</v>
       </c>
     </row>
     <row r="3">
@@ -6498,25 +6498,25 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0616</v>
+        <v>0.0149</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0385</v>
+        <v>0.6218</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0968</v>
+        <v>0.0848</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6284</v>
+        <v>0.1327</v>
       </c>
       <c r="F3" t="n">
-        <v>0.577</v>
+        <v>0.6046</v>
       </c>
       <c r="G3" t="n">
-        <v>0.423</v>
+        <v>0.3954</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0748</v>
+        <v>1.1308</v>
       </c>
     </row>
     <row r="4">
@@ -6524,25 +6524,25 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6596</v>
+        <v>-0.0148</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.089</v>
+        <v>0.4396</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1991</v>
+        <v>0.475</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0718</v>
+        <v>-0.0159</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6507</v>
+        <v>0.6165</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3493</v>
+        <v>0.3835</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2461</v>
+        <v>1.9926</v>
       </c>
     </row>
     <row r="5">
@@ -6576,25 +6576,25 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.054</v>
+        <v>0.0409</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2262</v>
+        <v>0.9154</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0309</v>
+        <v>-0.3274</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5738</v>
+        <v>0.2897</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5348</v>
+        <v>0.9677</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4652</v>
+        <v>0.0323</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3301</v>
+        <v>1.4742</v>
       </c>
     </row>
     <row r="7">
@@ -6602,25 +6602,25 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1729</v>
+        <v>0.2851</v>
       </c>
       <c r="C7" t="n">
-        <v>0.227</v>
+        <v>-0.0307</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3627</v>
+        <v>0.4845</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1737</v>
+        <v>0.1344</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6117</v>
+        <v>0.6056</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3883</v>
+        <v>0.3944</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7166</v>
+        <v>1.8094</v>
       </c>
     </row>
     <row r="8">
@@ -6628,25 +6628,25 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2851</v>
+        <v>0.6045</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0307</v>
+        <v>-0.0661</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4845</v>
+        <v>0.2066</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1344</v>
+        <v>0.1313</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6056</v>
+        <v>0.6573</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3944</v>
+        <v>0.3427</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8094</v>
+        <v>1.3609</v>
       </c>
     </row>
     <row r="9">
@@ -6654,25 +6654,25 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.6045</v>
+        <v>0.7182</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.0661</v>
+        <v>0.2436</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2066</v>
+        <v>0.0037</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1313</v>
+        <v>-0.1443</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6573</v>
+        <v>0.5735</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3427</v>
+        <v>0.4265</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3609</v>
+        <v>1.3154</v>
       </c>
     </row>
     <row r="10">
@@ -6680,25 +6680,25 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.0148</v>
+        <v>0.1729</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4396</v>
+        <v>0.227</v>
       </c>
       <c r="D10" t="n">
-        <v>0.475</v>
+        <v>0.3627</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0159</v>
+        <v>0.1737</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6165</v>
+        <v>0.6117</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3835</v>
+        <v>0.3883</v>
       </c>
       <c r="H10" t="n">
-        <v>1.9926</v>
+        <v>2.7166</v>
       </c>
     </row>
     <row r="11">
@@ -6706,25 +6706,25 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7182</v>
+        <v>0.6596</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2436</v>
+        <v>-0.089</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0037</v>
+        <v>0.1991</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1443</v>
+        <v>0.0718</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5735</v>
+        <v>0.6507</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4265</v>
+        <v>0.3493</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3154</v>
+        <v>1.2461</v>
       </c>
     </row>
     <row r="12">
@@ -6732,25 +6732,25 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0409</v>
+        <v>0.9049</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9154</v>
+        <v>-0.1415</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3274</v>
+        <v>-0.1511</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2897</v>
+        <v>-0.049</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9677</v>
+        <v>0.5702</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0323</v>
+        <v>0.4298</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4742</v>
+        <v>1.112</v>
       </c>
     </row>
     <row r="13">
@@ -6758,25 +6758,25 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0149</v>
+        <v>-0.054</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6218</v>
+        <v>0.2262</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0848</v>
+        <v>0.0309</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1327</v>
+        <v>0.5738</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6046</v>
+        <v>0.5348</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3954</v>
+        <v>0.4652</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1308</v>
+        <v>1.3301</v>
       </c>
     </row>
     <row r="14">
@@ -6784,25 +6784,25 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.1039</v>
+        <v>0.0616</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7835</v>
+        <v>0.0385</v>
       </c>
       <c r="D14" t="n">
-        <v>0.288</v>
+        <v>0.0968</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1853</v>
+        <v>0.6284</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6498</v>
+        <v>0.577</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3502</v>
+        <v>0.423</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4298</v>
+        <v>1.0748</v>
       </c>
     </row>
   </sheetData>
@@ -6838,13 +6838,13 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6171</v>
+        <v>0.659</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3808</v>
+        <v>0.4342</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6192</v>
+        <v>0.5658</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -6855,13 +6855,13 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5881</v>
+        <v>0.6391</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3459</v>
+        <v>0.4085</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6541</v>
+        <v>0.5915</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -6872,13 +6872,13 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7269</v>
+        <v>0.8574</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5283</v>
+        <v>0.7352</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4717</v>
+        <v>0.2648</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -6906,13 +6906,13 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.6935</v>
+        <v>0.6769</v>
       </c>
       <c r="C6" t="n">
-        <v>0.481</v>
+        <v>0.4582</v>
       </c>
       <c r="D6" t="n">
-        <v>0.519</v>
+        <v>0.5418</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -6923,13 +6923,13 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.5331</v>
+        <v>0.6528</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2842</v>
+        <v>0.4261</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7158</v>
+        <v>0.5739</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -6940,13 +6940,13 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.6528</v>
+        <v>0.6162</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4261</v>
+        <v>0.3797</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5739</v>
+        <v>0.6203</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -6957,13 +6957,13 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.6162</v>
+        <v>0.7972</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3797</v>
+        <v>0.6355</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6203</v>
+        <v>0.3645</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -6974,13 +6974,13 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8574</v>
+        <v>0.5331</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7352</v>
+        <v>0.2842</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2648</v>
+        <v>0.7158</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -6991,13 +6991,13 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7972</v>
+        <v>0.7269</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6355</v>
+        <v>0.5283</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3645</v>
+        <v>0.4717</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -7008,13 +7008,13 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.6769</v>
+        <v>0.6171</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4582</v>
+        <v>0.3808</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5418</v>
+        <v>0.6192</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -7025,13 +7025,13 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.6391</v>
+        <v>0.6935</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4085</v>
+        <v>0.481</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5915</v>
+        <v>0.519</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -7042,13 +7042,13 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.659</v>
+        <v>0.5881</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4342</v>
+        <v>0.3459</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5658</v>
+        <v>0.6541</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -7090,19 +7090,19 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2569</v>
+        <v>0.0944</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4427</v>
+        <v>0.6868</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4106</v>
+        <v>0.5654</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5894</v>
+        <v>0.4346</v>
       </c>
       <c r="F2" t="n">
-        <v>1.605</v>
+        <v>1.0378</v>
       </c>
     </row>
     <row r="3">
@@ -7110,19 +7110,19 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4175</v>
+        <v>-0.261</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2193</v>
+        <v>1.102</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3421</v>
+        <v>0.9065</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6579</v>
+        <v>0.0935</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5126</v>
+        <v>1.1118</v>
       </c>
     </row>
     <row r="4">
@@ -7130,19 +7130,19 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8944</v>
+        <v>0.731</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1426</v>
+        <v>0.1889</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6536</v>
+        <v>0.7505</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3464</v>
+        <v>0.2495</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0508</v>
+        <v>1.1329</v>
       </c>
     </row>
     <row r="5">
@@ -7170,19 +7170,19 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.4467</v>
+        <v>-0.0848</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3115</v>
+        <v>0.9302</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4785</v>
+        <v>0.7694</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5215</v>
+        <v>0.2306</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7867</v>
+        <v>1.0166</v>
       </c>
     </row>
     <row r="7">
@@ -7190,19 +7190,19 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.478</v>
+        <v>0.7513</v>
       </c>
       <c r="C7" t="n">
-        <v>0.084</v>
+        <v>-0.0755</v>
       </c>
       <c r="D7" t="n">
-        <v>0.288</v>
+        <v>0.496</v>
       </c>
       <c r="E7" t="n">
-        <v>0.712</v>
+        <v>0.504</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0617</v>
+        <v>1.0202</v>
       </c>
     </row>
     <row r="8">
@@ -7210,19 +7210,19 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7513</v>
+        <v>0.7244</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0755</v>
+        <v>-0.0849</v>
       </c>
       <c r="D8" t="n">
-        <v>0.496</v>
+        <v>0.4515</v>
       </c>
       <c r="E8" t="n">
-        <v>0.504</v>
+        <v>0.5485</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0202</v>
+        <v>1.0275</v>
       </c>
     </row>
     <row r="9">
@@ -7230,19 +7230,19 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.7244</v>
+        <v>0.815</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.0849</v>
+        <v>0.0132</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4515</v>
+        <v>0.6785</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5485</v>
+        <v>0.3215</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0275</v>
+        <v>1.0005</v>
       </c>
     </row>
     <row r="10">
@@ -7250,19 +7250,19 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.731</v>
+        <v>0.478</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1889</v>
+        <v>0.084</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7505</v>
+        <v>0.288</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2495</v>
+        <v>0.712</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1329</v>
+        <v>1.0617</v>
       </c>
     </row>
     <row r="11">
@@ -7270,19 +7270,19 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.815</v>
+        <v>0.8944</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0132</v>
+        <v>-0.1426</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6785</v>
+        <v>0.6536</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3215</v>
+        <v>0.3464</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0005</v>
+        <v>1.0508</v>
       </c>
     </row>
     <row r="12">
@@ -7290,19 +7290,19 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.0848</v>
+        <v>0.2569</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9302</v>
+        <v>0.4427</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7694</v>
+        <v>0.4106</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2306</v>
+        <v>0.5894</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0166</v>
+        <v>1.605</v>
       </c>
     </row>
     <row r="13">
@@ -7310,19 +7310,19 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.261</v>
+        <v>0.4467</v>
       </c>
       <c r="C13" t="n">
-        <v>1.102</v>
+        <v>0.3115</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9065</v>
+        <v>0.4785</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0935</v>
+        <v>0.5215</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1118</v>
+        <v>1.7867</v>
       </c>
     </row>
     <row r="14">
@@ -7330,19 +7330,19 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0944</v>
+        <v>0.4175</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6868</v>
+        <v>0.2193</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5654</v>
+        <v>0.3421</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4346</v>
+        <v>0.6579</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0378</v>
+        <v>1.5126</v>
       </c>
     </row>
   </sheetData>
@@ -7384,22 +7384,22 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.3145</v>
+        <v>0.0376</v>
       </c>
       <c r="C2" t="n">
-        <v>0.845</v>
+        <v>0.264</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2611</v>
+        <v>0.5474</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6995</v>
+        <v>0.5511</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3005</v>
+        <v>0.4489</v>
       </c>
       <c r="G2" t="n">
-        <v>1.4809</v>
+        <v>1.4524</v>
       </c>
     </row>
     <row r="3">
@@ -7407,22 +7407,22 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3788</v>
+        <v>-0.0645</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1128</v>
+        <v>0.0224</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2002</v>
+        <v>0.9723</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3447</v>
+        <v>0.911</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6553</v>
+        <v>0.089</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7235</v>
+        <v>1.0099</v>
       </c>
     </row>
     <row r="4">
@@ -7430,22 +7430,22 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.43</v>
+        <v>0.8889</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6046</v>
+        <v>-0.1187</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2135</v>
+        <v>0.2355</v>
       </c>
       <c r="E4" t="n">
-        <v>0.699</v>
+        <v>0.8991</v>
       </c>
       <c r="F4" t="n">
-        <v>0.301</v>
+        <v>0.1009</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0911</v>
+        <v>1.1776</v>
       </c>
     </row>
     <row r="5">
@@ -7476,22 +7476,22 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0503</v>
+        <v>0.2097</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6089</v>
+        <v>-0.1696</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1781</v>
+        <v>0.9087</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5628</v>
+        <v>0.8773</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4372</v>
+        <v>0.1227</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1845</v>
+        <v>1.1792</v>
       </c>
     </row>
     <row r="7">
@@ -7499,22 +7499,22 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.001</v>
+        <v>0.7214</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6608</v>
+        <v>0.0442</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0393</v>
+        <v>-0.0334</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4107</v>
+        <v>0.5386</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5893</v>
+        <v>0.4614</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0071</v>
+        <v>1.0118</v>
       </c>
     </row>
     <row r="8">
@@ -7522,22 +7522,22 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7214</v>
+        <v>0.8003</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0442</v>
+        <v>-0.0896</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0334</v>
+        <v>-0.0163</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5386</v>
+        <v>0.5488</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4614</v>
+        <v>0.4512</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0118</v>
+        <v>1.0259</v>
       </c>
     </row>
     <row r="9">
@@ -7545,22 +7545,22 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.8003</v>
+        <v>0.7852</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.0896</v>
+        <v>0.0676</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0163</v>
+        <v>0.0479</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5488</v>
+        <v>0.7284</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4512</v>
+        <v>0.2716</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0259</v>
+        <v>1.0223</v>
       </c>
     </row>
     <row r="10">
@@ -7568,22 +7568,22 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8889</v>
+        <v>-0.001</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.1187</v>
+        <v>0.6608</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2355</v>
+        <v>-0.0393</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8991</v>
+        <v>0.4107</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1009</v>
+        <v>0.5893</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1776</v>
+        <v>1.0071</v>
       </c>
     </row>
     <row r="11">
@@ -7591,22 +7591,22 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7852</v>
+        <v>0.43</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0676</v>
+        <v>0.6046</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0479</v>
+        <v>-0.2135</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7284</v>
+        <v>0.699</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2716</v>
+        <v>0.301</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0223</v>
+        <v>2.0911</v>
       </c>
     </row>
     <row r="12">
@@ -7614,22 +7614,22 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2097</v>
+        <v>-0.3145</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1696</v>
+        <v>0.845</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9087</v>
+        <v>0.2611</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8773</v>
+        <v>0.6995</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1227</v>
+        <v>0.3005</v>
       </c>
       <c r="G12" t="n">
-        <v>1.1792</v>
+        <v>1.4809</v>
       </c>
     </row>
     <row r="13">
@@ -7637,22 +7637,22 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.0645</v>
+        <v>0.0503</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0224</v>
+        <v>0.6089</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9723</v>
+        <v>0.1781</v>
       </c>
       <c r="E13" t="n">
-        <v>0.911</v>
+        <v>0.5628</v>
       </c>
       <c r="F13" t="n">
-        <v>0.089</v>
+        <v>0.4372</v>
       </c>
       <c r="G13" t="n">
-        <v>1.0099</v>
+        <v>1.1845</v>
       </c>
     </row>
     <row r="14">
@@ -7660,22 +7660,22 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0376</v>
+        <v>0.3788</v>
       </c>
       <c r="C14" t="n">
-        <v>0.264</v>
+        <v>0.1128</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5474</v>
+        <v>0.2002</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5511</v>
+        <v>0.3447</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4489</v>
+        <v>0.6553</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4524</v>
+        <v>1.7235</v>
       </c>
     </row>
   </sheetData>
@@ -7720,25 +7720,25 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.207</v>
+        <v>0.1094</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7692</v>
+        <v>0.2283</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2968</v>
+        <v>0.7245</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.082</v>
+        <v>-0.2419</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6695</v>
+        <v>0.7477</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3305</v>
+        <v>0.2523</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4786</v>
+        <v>1.4878</v>
       </c>
     </row>
     <row r="3">
@@ -7746,25 +7746,25 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1112</v>
+        <v>-0.0422</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1691</v>
+        <v>0.0226</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0593</v>
+        <v>0.8853</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6228</v>
+        <v>0.0668</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6069</v>
+        <v>0.8101</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3931</v>
+        <v>0.1899</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2345</v>
+        <v>1.0173</v>
       </c>
     </row>
     <row r="4">
@@ -7772,25 +7772,25 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5362</v>
+        <v>0.8002</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5331</v>
+        <v>-0.0836</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1234</v>
+        <v>0.2503</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1776</v>
+        <v>0.0634</v>
       </c>
       <c r="F4" t="n">
-        <v>0.717</v>
+        <v>0.8436</v>
       </c>
       <c r="G4" t="n">
-        <v>0.283</v>
+        <v>0.1564</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3229</v>
+        <v>1.2314</v>
       </c>
     </row>
     <row r="5">
@@ -7824,25 +7824,25 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.016</v>
+        <v>0.1024</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5978</v>
+        <v>-0.1348</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1701</v>
+        <v>0.8063</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1275</v>
+        <v>0.2645</v>
       </c>
       <c r="F6" t="n">
-        <v>0.572</v>
+        <v>0.8362</v>
       </c>
       <c r="G6" t="n">
-        <v>0.428</v>
+        <v>0.1638</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2596</v>
+        <v>1.3098</v>
       </c>
     </row>
     <row r="7">
@@ -7850,25 +7850,25 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.1125</v>
+        <v>0.7163</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7064</v>
+        <v>0.0341</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0951</v>
+        <v>-0.0428</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2505</v>
+        <v>0.0861</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4958</v>
+        <v>0.5718</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5042</v>
+        <v>0.4282</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3445</v>
+        <v>1.0408</v>
       </c>
     </row>
     <row r="8">
@@ -7876,25 +7876,25 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7163</v>
+        <v>0.8244</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0341</v>
+        <v>-0.1137</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0428</v>
+        <v>0.0347</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0861</v>
+        <v>-0.066</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5718</v>
+        <v>0.569</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4282</v>
+        <v>0.431</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0408</v>
+        <v>1.0547</v>
       </c>
     </row>
     <row r="9">
@@ -7902,25 +7902,25 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.8244</v>
+        <v>0.7652</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.1137</v>
+        <v>0.035</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0347</v>
+        <v>0.0095</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.066</v>
+        <v>0.2061</v>
       </c>
       <c r="F9" t="n">
-        <v>0.569</v>
+        <v>0.7992</v>
       </c>
       <c r="G9" t="n">
-        <v>0.431</v>
+        <v>0.2008</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0547</v>
+        <v>1.1492</v>
       </c>
     </row>
     <row r="10">
@@ -7928,25 +7928,25 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8002</v>
+        <v>-0.1125</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0836</v>
+        <v>0.7064</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2503</v>
+        <v>-0.0951</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0634</v>
+        <v>0.2505</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8436</v>
+        <v>0.4958</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1564</v>
+        <v>0.5042</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2314</v>
+        <v>1.3445</v>
       </c>
     </row>
     <row r="11">
@@ -7954,25 +7954,25 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7652</v>
+        <v>0.5362</v>
       </c>
       <c r="C11" t="n">
-        <v>0.035</v>
+        <v>0.5331</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0095</v>
+        <v>-0.1234</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2061</v>
+        <v>-0.1776</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7992</v>
+        <v>0.717</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2008</v>
+        <v>0.283</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1492</v>
+        <v>2.3229</v>
       </c>
     </row>
     <row r="12">
@@ -7980,25 +7980,25 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1024</v>
+        <v>-0.207</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1348</v>
+        <v>0.7692</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8063</v>
+        <v>0.2968</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2645</v>
+        <v>-0.082</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8362</v>
+        <v>0.6695</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1638</v>
+        <v>0.3305</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3098</v>
+        <v>1.4786</v>
       </c>
     </row>
     <row r="13">
@@ -8006,25 +8006,25 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.0422</v>
+        <v>0.016</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0226</v>
+        <v>0.5978</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8853</v>
+        <v>0.1701</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0668</v>
+        <v>0.1275</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8101</v>
+        <v>0.572</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1899</v>
+        <v>0.428</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0173</v>
+        <v>1.2596</v>
       </c>
     </row>
     <row r="14">
@@ -8032,25 +8032,25 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1094</v>
+        <v>0.1112</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2283</v>
+        <v>0.1691</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7245</v>
+        <v>0.0593</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2419</v>
+        <v>0.6228</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7477</v>
+        <v>0.6069</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2523</v>
+        <v>0.3931</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4878</v>
+        <v>1.2345</v>
       </c>
     </row>
   </sheetData>
@@ -8086,13 +8086,13 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5658</v>
+        <v>0.6541</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3202</v>
+        <v>0.4279</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6798</v>
+        <v>0.5721</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -8103,13 +8103,13 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6903</v>
+        <v>0.6665</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4766</v>
+        <v>0.4442</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5234</v>
+        <v>0.5558</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -8120,13 +8120,13 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6219</v>
+        <v>0.6579</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3867</v>
+        <v>0.4328</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6133</v>
+        <v>0.5672</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -8154,13 +8154,13 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.641</v>
+        <v>0.7188</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4108</v>
+        <v>0.5167</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5892</v>
+        <v>0.4833</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -8171,13 +8171,13 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.5917</v>
+        <v>0.549</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3501</v>
+        <v>0.3014</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6499</v>
+        <v>0.6986</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -8188,13 +8188,13 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.549</v>
+        <v>0.6292</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3014</v>
+        <v>0.3959</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6986</v>
+        <v>0.6041</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -8205,13 +8205,13 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.6292</v>
+        <v>0.7172</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3959</v>
+        <v>0.5144</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6041</v>
+        <v>0.4856</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -8222,13 +8222,13 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.6579</v>
+        <v>0.5917</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4328</v>
+        <v>0.3501</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5672</v>
+        <v>0.6499</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -8239,13 +8239,13 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7172</v>
+        <v>0.6219</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5144</v>
+        <v>0.3867</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4856</v>
+        <v>0.6133</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -8256,13 +8256,13 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.7188</v>
+        <v>0.5658</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5167</v>
+        <v>0.3202</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4833</v>
+        <v>0.6798</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -8273,13 +8273,13 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.6665</v>
+        <v>0.641</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4442</v>
+        <v>0.4108</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5558</v>
+        <v>0.5892</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -8290,13 +8290,13 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6541</v>
+        <v>0.6903</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4279</v>
+        <v>0.4766</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5721</v>
+        <v>0.5234</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -8338,19 +8338,19 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6888</v>
+        <v>-0.0493</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0855</v>
+        <v>0.8094</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4025</v>
+        <v>0.6039</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5975</v>
+        <v>0.3961</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0308</v>
+        <v>1.0074</v>
       </c>
     </row>
     <row r="3">
@@ -8358,19 +8358,19 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4263</v>
+        <v>-0.188</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3178</v>
+        <v>0.991</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4649</v>
+        <v>0.7669</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5351</v>
+        <v>0.2331</v>
       </c>
       <c r="F3" t="n">
-        <v>1.849</v>
+        <v>1.0719</v>
       </c>
     </row>
     <row r="4">
@@ -8378,19 +8378,19 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8244</v>
+        <v>0.3443</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1594</v>
+        <v>0.3716</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5283</v>
+        <v>0.4288</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4717</v>
+        <v>0.5712</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0747</v>
+        <v>1.9884</v>
       </c>
     </row>
     <row r="5">
@@ -8418,19 +8418,19 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.4064</v>
+        <v>-0.0843</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2845</v>
+        <v>0.9362</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4016</v>
+        <v>0.7774</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5984</v>
+        <v>0.2226</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7902</v>
+        <v>1.0162</v>
       </c>
     </row>
     <row r="7">
@@ -8438,19 +8438,19 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4147</v>
+        <v>0.4757</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2141</v>
+        <v>0.1044</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3372</v>
+        <v>0.3039</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6628</v>
+        <v>0.6961</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4977</v>
+        <v>1.0961</v>
       </c>
     </row>
     <row r="8">
@@ -8458,19 +8458,19 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.4757</v>
+        <v>0.8377</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1044</v>
+        <v>-0.1644</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3039</v>
+        <v>0.5435</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6961</v>
+        <v>0.4565</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0961</v>
+        <v>1.0769</v>
       </c>
     </row>
     <row r="9">
@@ -8478,19 +8478,19 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.8377</v>
+        <v>0.6087</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.1644</v>
+        <v>0.1618</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5435</v>
+        <v>0.5292</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4565</v>
+        <v>0.4708</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0769</v>
+        <v>1.1406</v>
       </c>
     </row>
     <row r="10">
@@ -8498,19 +8498,19 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.3443</v>
+        <v>0.4147</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3716</v>
+        <v>0.2141</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4288</v>
+        <v>0.3372</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5712</v>
+        <v>0.6628</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9884</v>
+        <v>1.4977</v>
       </c>
     </row>
     <row r="11">
@@ -8518,19 +8518,19 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6087</v>
+        <v>0.8244</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1618</v>
+        <v>-0.1594</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5292</v>
+        <v>0.5283</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4708</v>
+        <v>0.4717</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1406</v>
+        <v>1.0747</v>
       </c>
     </row>
     <row r="12">
@@ -8538,19 +8538,19 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.0843</v>
+        <v>0.6888</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9362</v>
+        <v>-0.0855</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7774</v>
+        <v>0.4025</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2226</v>
+        <v>0.5975</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0162</v>
+        <v>1.0308</v>
       </c>
     </row>
     <row r="13">
@@ -8558,19 +8558,19 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.188</v>
+        <v>0.4064</v>
       </c>
       <c r="C13" t="n">
-        <v>0.991</v>
+        <v>0.2845</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7669</v>
+        <v>0.4016</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2331</v>
+        <v>0.5984</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0719</v>
+        <v>1.7902</v>
       </c>
     </row>
     <row r="14">
@@ -8578,19 +8578,19 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.0493</v>
+        <v>0.4263</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8094</v>
+        <v>0.3178</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6039</v>
+        <v>0.4649</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3961</v>
+        <v>0.5351</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0074</v>
+        <v>1.849</v>
       </c>
     </row>
   </sheetData>
@@ -8632,22 +8632,22 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9279</v>
+        <v>-0.0355</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0196</v>
+        <v>0.7233</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2826</v>
+        <v>0.107</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5878</v>
+        <v>0.5848</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4122</v>
+        <v>0.4152</v>
       </c>
       <c r="G2" t="n">
-        <v>1.1849</v>
+        <v>1.0487</v>
       </c>
     </row>
     <row r="3">
@@ -8655,22 +8655,22 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4329</v>
+        <v>-0.0816</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3225</v>
+        <v>0.9479</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0214</v>
+        <v>-0.0281</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4763</v>
+        <v>0.7886</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5237</v>
+        <v>0.2114</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8544</v>
+        <v>1.0166</v>
       </c>
     </row>
     <row r="4">
@@ -8678,22 +8678,22 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7921</v>
+        <v>-0.3424</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1242</v>
+        <v>0.1843</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0331</v>
+        <v>1.056</v>
       </c>
       <c r="E4" t="n">
-        <v>0.557</v>
+        <v>0.9377</v>
       </c>
       <c r="F4" t="n">
-        <v>0.443</v>
+        <v>0.0623</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0528</v>
+        <v>1.2743</v>
       </c>
     </row>
     <row r="5">
@@ -8724,22 +8724,22 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5259</v>
+        <v>-0.0212</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3251</v>
+        <v>0.8796</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1354</v>
+        <v>0.0345</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4629</v>
+        <v>0.7854</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5371</v>
+        <v>0.2146</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8235</v>
+        <v>1.0042</v>
       </c>
     </row>
     <row r="7">
@@ -8747,22 +8747,22 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2898</v>
+        <v>0.0769</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1799</v>
+        <v>-0.0201</v>
       </c>
       <c r="D7" t="n">
-        <v>0.202</v>
+        <v>0.609</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3336</v>
+        <v>0.4224</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6664</v>
+        <v>0.5776</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5288</v>
+        <v>1.0341</v>
       </c>
     </row>
     <row r="8">
@@ -8770,22 +8770,22 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0769</v>
+        <v>0.5092</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0201</v>
+        <v>-0.2293</v>
       </c>
       <c r="D8" t="n">
-        <v>0.609</v>
+        <v>0.4642</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4224</v>
+        <v>0.5783</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5776</v>
+        <v>0.4217</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0341</v>
+        <v>2.3885</v>
       </c>
     </row>
     <row r="9">
@@ -8793,22 +8793,22 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5092</v>
+        <v>0.4341</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.2293</v>
+        <v>0.1261</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4642</v>
+        <v>0.2618</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5783</v>
+        <v>0.5199</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4217</v>
+        <v>0.4801</v>
       </c>
       <c r="G9" t="n">
-        <v>2.3885</v>
+        <v>1.8401</v>
       </c>
     </row>
     <row r="10">
@@ -8816,22 +8816,22 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.3424</v>
+        <v>0.2898</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1843</v>
+        <v>0.1799</v>
       </c>
       <c r="D10" t="n">
-        <v>1.056</v>
+        <v>0.202</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9377</v>
+        <v>0.3336</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0623</v>
+        <v>0.6664</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2743</v>
+        <v>2.5288</v>
       </c>
     </row>
     <row r="11">
@@ -8839,22 +8839,22 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.4341</v>
+        <v>0.7921</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1261</v>
+        <v>-0.1242</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2618</v>
+        <v>0.0331</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5199</v>
+        <v>0.557</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4801</v>
+        <v>0.443</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8401</v>
+        <v>1.0528</v>
       </c>
     </row>
     <row r="12">
@@ -8862,22 +8862,22 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.0212</v>
+        <v>0.9279</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8796</v>
+        <v>-0.0196</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0345</v>
+        <v>-0.2826</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7854</v>
+        <v>0.5878</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2146</v>
+        <v>0.4122</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0042</v>
+        <v>1.1849</v>
       </c>
     </row>
     <row r="13">
@@ -8885,22 +8885,22 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.0816</v>
+        <v>0.5259</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9479</v>
+        <v>0.3251</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0281</v>
+        <v>-0.1354</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7886</v>
+        <v>0.4629</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2114</v>
+        <v>0.5371</v>
       </c>
       <c r="G13" t="n">
-        <v>1.0166</v>
+        <v>1.8235</v>
       </c>
     </row>
     <row r="14">
@@ -8908,22 +8908,22 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.0355</v>
+        <v>0.4329</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7233</v>
+        <v>0.3225</v>
       </c>
       <c r="D14" t="n">
-        <v>0.107</v>
+        <v>0.0214</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5848</v>
+        <v>0.4763</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4152</v>
+        <v>0.5237</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0487</v>
+        <v>1.8544</v>
       </c>
     </row>
   </sheetData>
@@ -8968,25 +8968,25 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0144</v>
+        <v>0.6698</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6091</v>
+        <v>-0.0133</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3604</v>
+        <v>0.0949</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3224</v>
+        <v>0.0817</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6175</v>
+        <v>0.5796</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3825</v>
+        <v>0.4204</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2142</v>
+        <v>1.0713</v>
       </c>
     </row>
     <row r="3">
@@ -8994,25 +8994,25 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1693</v>
+        <v>0.8324</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0115</v>
+        <v>-0.1257</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5836</v>
+        <v>0.1544</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0676</v>
+        <v>-0.0012</v>
       </c>
       <c r="F3" t="n">
-        <v>0.536</v>
+        <v>0.7592</v>
       </c>
       <c r="G3" t="n">
-        <v>0.464</v>
+        <v>0.2408</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1968</v>
+        <v>1.1158</v>
       </c>
     </row>
     <row r="4">
@@ -9020,25 +9020,25 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.0969</v>
+        <v>0.2463</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5288</v>
+        <v>0.0953</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3437</v>
+        <v>-0.1126</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0085</v>
+        <v>0.7611</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5421</v>
+        <v>0.7991</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4579</v>
+        <v>0.2009</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7978</v>
+        <v>1.2897</v>
       </c>
     </row>
     <row r="5">
@@ -9072,25 +9072,25 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1864</v>
+        <v>0.9226</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0783</v>
+        <v>0.0838</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5792</v>
+        <v>-0.0357</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0917</v>
+        <v>-0.0284</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5082</v>
+        <v>0.8629</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4918</v>
+        <v>0.1371</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3001</v>
+        <v>1.0215</v>
       </c>
     </row>
     <row r="7">
@@ -9098,25 +9098,25 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0069</v>
+        <v>-0.1287</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0882</v>
+        <v>-0.0251</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5586</v>
+        <v>0.2974</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2689</v>
+        <v>0.6412</v>
       </c>
       <c r="F7" t="n">
-        <v>0.438</v>
+        <v>0.5346</v>
       </c>
       <c r="G7" t="n">
-        <v>0.562</v>
+        <v>0.4654</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4982</v>
+        <v>1.5077</v>
       </c>
     </row>
     <row r="8">
@@ -9124,25 +9124,25 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.1287</v>
+        <v>-0.0622</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0251</v>
+        <v>0.8606</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2974</v>
+        <v>-0.2135</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6412</v>
+        <v>0.3051</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5346</v>
+        <v>0.7863</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4654</v>
+        <v>0.2137</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5077</v>
+        <v>1.3946</v>
       </c>
     </row>
     <row r="9">
@@ -9150,25 +9150,25 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0622</v>
+        <v>0.2156</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8606</v>
+        <v>0.5128</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2135</v>
+        <v>0.0345</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3051</v>
+        <v>0.1499</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7863</v>
+        <v>0.5592</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2137</v>
+        <v>0.4408</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3946</v>
+        <v>1.5451</v>
       </c>
     </row>
     <row r="10">
@@ -9176,25 +9176,25 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2463</v>
+        <v>0.0069</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0953</v>
+        <v>-0.0882</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1126</v>
+        <v>0.5586</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7611</v>
+        <v>0.2689</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7991</v>
+        <v>0.438</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2009</v>
+        <v>0.562</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2897</v>
+        <v>1.4982</v>
       </c>
     </row>
     <row r="11">
@@ -9202,25 +9202,25 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2156</v>
+        <v>-0.0969</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5128</v>
+        <v>0.5288</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0345</v>
+        <v>0.3437</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1499</v>
+        <v>-0.0085</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5592</v>
+        <v>0.5421</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4408</v>
+        <v>0.4579</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5451</v>
+        <v>1.7978</v>
       </c>
     </row>
     <row r="12">
@@ -9228,25 +9228,25 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.9226</v>
+        <v>0.0144</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0838</v>
+        <v>0.6091</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0357</v>
+        <v>0.3604</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0284</v>
+        <v>-0.3224</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8629</v>
+        <v>0.6175</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1371</v>
+        <v>0.3825</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0215</v>
+        <v>2.2142</v>
       </c>
     </row>
     <row r="13">
@@ -9254,25 +9254,25 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.8324</v>
+        <v>0.1864</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.1257</v>
+        <v>0.0783</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1544</v>
+        <v>0.5792</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0012</v>
+        <v>-0.0917</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7592</v>
+        <v>0.5082</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2408</v>
+        <v>0.4918</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1158</v>
+        <v>1.3001</v>
       </c>
     </row>
     <row r="14">
@@ -9280,25 +9280,25 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6698</v>
+        <v>0.1693</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.0133</v>
+        <v>0.0115</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0949</v>
+        <v>0.5836</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0817</v>
+        <v>0.0676</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5796</v>
+        <v>0.536</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4204</v>
+        <v>0.464</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0713</v>
+        <v>1.1968</v>
       </c>
     </row>
   </sheetData>
@@ -9334,13 +9334,13 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3744</v>
+        <v>0.7673</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1402</v>
+        <v>0.5887</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8598</v>
+        <v>0.4113</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -9351,13 +9351,13 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6886</v>
+        <v>0.7008</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4742</v>
+        <v>0.4912</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5258</v>
+        <v>0.5088</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -9368,13 +9368,13 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4892</v>
+        <v>0.6718</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2393</v>
+        <v>0.4512</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7607</v>
+        <v>0.5488</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -9402,13 +9402,13 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.532</v>
+        <v>0.8368</v>
       </c>
       <c r="C6" t="n">
-        <v>0.283</v>
+        <v>0.7003</v>
       </c>
       <c r="D6" t="n">
-        <v>0.717</v>
+        <v>0.2997</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -9419,13 +9419,13 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4571</v>
+        <v>0.353</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2089</v>
+        <v>0.1246</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7911</v>
+        <v>0.8754</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -9436,13 +9436,13 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.353</v>
+        <v>0.4873</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1246</v>
+        <v>0.2374</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8754</v>
+        <v>0.7626</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -9453,13 +9453,13 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4873</v>
+        <v>0.6006</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2374</v>
+        <v>0.3608</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7626</v>
+        <v>0.6392</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -9470,13 +9470,13 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.6718</v>
+        <v>0.4571</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4512</v>
+        <v>0.2089</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5488</v>
+        <v>0.7911</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -9487,13 +9487,13 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6006</v>
+        <v>0.4892</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3608</v>
+        <v>0.2393</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6392</v>
+        <v>0.7607</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -9504,13 +9504,13 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8368</v>
+        <v>0.3744</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7003</v>
+        <v>0.1402</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2997</v>
+        <v>0.8598</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -9521,13 +9521,13 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.7008</v>
+        <v>0.532</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4912</v>
+        <v>0.283</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5088</v>
+        <v>0.717</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -9538,13 +9538,13 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.7673</v>
+        <v>0.6886</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5887</v>
+        <v>0.4742</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4113</v>
+        <v>0.5258</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -9586,19 +9586,19 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2605</v>
+        <v>0.9154</v>
       </c>
       <c r="C2" t="n">
-        <v>0.147</v>
+        <v>-0.1068</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1339</v>
+        <v>0.7357</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8661</v>
+        <v>0.2643</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5778</v>
+        <v>1.0272</v>
       </c>
     </row>
     <row r="3">
@@ -9606,19 +9606,19 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5141</v>
+        <v>0.9858</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2315</v>
+        <v>-0.2668</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4562</v>
+        <v>0.7375</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5438</v>
+        <v>0.2625</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3896</v>
+        <v>1.1458</v>
       </c>
     </row>
     <row r="4">
@@ -9626,19 +9626,19 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1283</v>
+        <v>0.1931</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4602</v>
+        <v>0.6227</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2969</v>
+        <v>0.5647</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7031</v>
+        <v>0.4353</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1546</v>
+        <v>1.1905</v>
       </c>
     </row>
     <row r="5">
@@ -9666,19 +9666,19 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5423</v>
+        <v>1.0299</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0043</v>
+        <v>-0.1453</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2968</v>
+        <v>0.908</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7032</v>
+        <v>0.092</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0001</v>
+        <v>1.0398</v>
       </c>
     </row>
     <row r="7">
@@ -9686,19 +9686,19 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2508</v>
+        <v>-0.3256</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2722</v>
+        <v>0.8682</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2163</v>
+        <v>0.5315</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7837</v>
+        <v>0.4685</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9868</v>
+        <v>1.2757</v>
       </c>
     </row>
     <row r="8">
@@ -9706,19 +9706,19 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.3256</v>
+        <v>-0.092</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8682</v>
+        <v>0.7443</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5315</v>
+        <v>0.4828</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4685</v>
+        <v>0.5172</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2757</v>
+        <v>1.0306</v>
       </c>
     </row>
     <row r="9">
@@ -9726,19 +9726,19 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.092</v>
+        <v>0.5394</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7443</v>
+        <v>0.1015</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4828</v>
+        <v>0.3649</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5172</v>
+        <v>0.6351</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0306</v>
+        <v>1.0707</v>
       </c>
     </row>
     <row r="10">
@@ -9746,19 +9746,19 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1931</v>
+        <v>0.2508</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6227</v>
+        <v>0.2722</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5647</v>
+        <v>0.2163</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4353</v>
+        <v>0.7837</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1905</v>
+        <v>1.9868</v>
       </c>
     </row>
     <row r="11">
@@ -9766,19 +9766,19 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5394</v>
+        <v>0.1283</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1015</v>
+        <v>0.4602</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3649</v>
+        <v>0.2969</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6351</v>
+        <v>0.7031</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0707</v>
+        <v>1.1546</v>
       </c>
     </row>
     <row r="12">
@@ -9786,19 +9786,19 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>1.0299</v>
+        <v>0.2605</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1453</v>
+        <v>0.147</v>
       </c>
       <c r="D12" t="n">
-        <v>0.908</v>
+        <v>0.1339</v>
       </c>
       <c r="E12" t="n">
-        <v>0.092</v>
+        <v>0.8661</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0398</v>
+        <v>1.5778</v>
       </c>
     </row>
     <row r="13">
@@ -9806,19 +9806,19 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.9858</v>
+        <v>0.5423</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.2668</v>
+        <v>0.0043</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7375</v>
+        <v>0.2968</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2625</v>
+        <v>0.7032</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1458</v>
+        <v>1.0001</v>
       </c>
     </row>
     <row r="14">
@@ -9826,19 +9826,19 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.9154</v>
+        <v>0.5141</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.1068</v>
+        <v>0.2315</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7357</v>
+        <v>0.4562</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2643</v>
+        <v>0.5438</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0272</v>
+        <v>1.3896</v>
       </c>
     </row>
   </sheetData>
@@ -9880,22 +9880,22 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0731</v>
+        <v>0.9821</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2192</v>
+        <v>0.0987</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6718</v>
+        <v>-0.2506</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4213</v>
+        <v>0.8586</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5787</v>
+        <v>0.1414</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2364</v>
+        <v>1.151</v>
       </c>
     </row>
     <row r="3">
@@ -9903,22 +9903,22 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5254</v>
+        <v>0.9246</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2442</v>
+        <v>-0.1512</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0428</v>
+        <v>-0.0451</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4748</v>
+        <v>0.728</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5252</v>
+        <v>0.272</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4282</v>
+        <v>1.0583</v>
       </c>
     </row>
     <row r="4">
@@ -9926,22 +9926,22 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.0604</v>
+        <v>0.3045</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0729</v>
+        <v>0.6964</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7468</v>
+        <v>-0.0861</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5626</v>
+        <v>0.6886</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4374</v>
+        <v>0.3114</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0322</v>
+        <v>1.4038</v>
       </c>
     </row>
     <row r="5">
@@ -9972,22 +9972,22 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.4371</v>
+        <v>0.9262</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.1609</v>
+        <v>-0.1375</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3277</v>
+        <v>0.1335</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3628</v>
+        <v>0.8939</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6372</v>
+        <v>0.1061</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1599</v>
+        <v>1.0865</v>
       </c>
     </row>
     <row r="7">
@@ -9995,22 +9995,22 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2856</v>
+        <v>-0.2122</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3136</v>
+        <v>0.9601</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0297</v>
+        <v>-0.0755</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2399</v>
+        <v>0.7602</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7601</v>
+        <v>0.2398</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0021</v>
+        <v>1.1104</v>
       </c>
     </row>
     <row r="8">
@@ -10018,22 +10018,22 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.2122</v>
+        <v>-0.1459</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9601</v>
+        <v>0.4351</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0755</v>
+        <v>0.5023</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7602</v>
+        <v>0.5134</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2398</v>
+        <v>0.4866</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1104</v>
+        <v>2.1439</v>
       </c>
     </row>
     <row r="9">
@@ -10041,22 +10041,22 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.1459</v>
+        <v>0.5101</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4351</v>
+        <v>0.0876</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5023</v>
+        <v>0.0838</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5134</v>
+        <v>0.3597</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4866</v>
+        <v>0.6403</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1439</v>
+        <v>1.1143</v>
       </c>
     </row>
     <row r="10">
@@ -10064,22 +10064,22 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.3045</v>
+        <v>0.2856</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6964</v>
+        <v>0.3136</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0861</v>
+        <v>-0.0297</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6886</v>
+        <v>0.2399</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3114</v>
+        <v>0.7601</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4038</v>
+        <v>2.0021</v>
       </c>
     </row>
     <row r="11">
@@ -10087,22 +10087,22 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5101</v>
+        <v>-0.0604</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0876</v>
+        <v>0.0729</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0838</v>
+        <v>0.7468</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3597</v>
+        <v>0.5626</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6403</v>
+        <v>0.4374</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1143</v>
+        <v>1.0322</v>
       </c>
     </row>
     <row r="12">
@@ -10110,22 +10110,22 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.9262</v>
+        <v>0.0731</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1375</v>
+        <v>-0.2192</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1335</v>
+        <v>0.6718</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8939</v>
+        <v>0.4213</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1061</v>
+        <v>0.5787</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0865</v>
+        <v>1.2364</v>
       </c>
     </row>
     <row r="13">
@@ -10133,22 +10133,22 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.9246</v>
+        <v>0.4371</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.1512</v>
+        <v>-0.1609</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0451</v>
+        <v>0.3277</v>
       </c>
       <c r="E13" t="n">
-        <v>0.728</v>
+        <v>0.3628</v>
       </c>
       <c r="F13" t="n">
-        <v>0.272</v>
+        <v>0.6372</v>
       </c>
       <c r="G13" t="n">
-        <v>1.0583</v>
+        <v>2.1599</v>
       </c>
     </row>
     <row r="14">
@@ -10156,22 +10156,22 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.9821</v>
+        <v>0.5254</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0987</v>
+        <v>0.2442</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2506</v>
+        <v>0.0428</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8586</v>
+        <v>0.4748</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1414</v>
+        <v>0.5252</v>
       </c>
       <c r="G14" t="n">
-        <v>1.151</v>
+        <v>1.4282</v>
       </c>
     </row>
   </sheetData>

--- a/Reproduce6 - AnalysisBySystem/Data_Analysis/generatedData/EFA_Summary_Consolidated.xlsx
+++ b/Reproduce6 - AnalysisBySystem/Data_Analysis/generatedData/EFA_Summary_Consolidated.xlsx
@@ -161,43 +161,43 @@
     <t xml:space="preserve">Complexity</t>
   </si>
   <si>
-    <t xml:space="preserve">analysisConfigure</t>
+    <t xml:space="preserve">CogSysEnjoy</t>
   </si>
   <si>
-    <t xml:space="preserve">sysEasyStart</t>
+    <t xml:space="preserve">CogSysThinkDeep</t>
   </si>
   <si>
-    <t xml:space="preserve">sysEnjoy</t>
+    <t xml:space="preserve">CogSysUseful</t>
   </si>
   <si>
-    <t xml:space="preserve">sysRetrieveInfo</t>
+    <t xml:space="preserve">CogTaskComplete</t>
   </si>
   <si>
-    <t xml:space="preserve">sysSimpleUnderstand</t>
+    <t xml:space="preserve">IntAnalysisConfigure</t>
   </si>
   <si>
-    <t xml:space="preserve">sysThinkDeep</t>
+    <t xml:space="preserve">IntSysEasyStart</t>
   </si>
   <si>
-    <t xml:space="preserve">sysUseful</t>
+    <t xml:space="preserve">IntSysSimpleUnderstand</t>
   </si>
   <si>
-    <t xml:space="preserve">taskComplete</t>
+    <t xml:space="preserve">VisAppropriate</t>
   </si>
   <si>
-    <t xml:space="preserve">trialError</t>
+    <t xml:space="preserve">VisFaithful</t>
   </si>
   <si>
-    <t xml:space="preserve">visAppropriate</t>
+    <t xml:space="preserve">VisRemember</t>
   </si>
   <si>
-    <t xml:space="preserve">visFaithful</t>
+    <t xml:space="preserve">VisSimpleUnderstand</t>
   </si>
   <si>
-    <t xml:space="preserve">visRemember</t>
+    <t xml:space="preserve">VisSysRetrieveInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">visSimpleUnderstand</t>
+    <t xml:space="preserve">VisTrialError</t>
   </si>
   <si>
     <t xml:space="preserve">Loading_F2</t>
@@ -596,25 +596,25 @@
         <v>5.41</v>
       </c>
       <c r="G2" t="n">
-        <v>0.752</v>
+        <v>0.742</v>
       </c>
       <c r="H2" t="n">
         <v>0.888</v>
       </c>
       <c r="I2" t="n">
-        <v>0.365</v>
+        <v>0.366</v>
       </c>
       <c r="J2" t="n">
         <v>0.533</v>
       </c>
       <c r="K2" t="n">
-        <v>0.28</v>
+        <v>0.273</v>
       </c>
       <c r="L2" t="n">
         <v>0.283</v>
       </c>
       <c r="M2" t="n">
-        <v>0.202</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="3">
@@ -637,25 +637,25 @@
         <v>4.609</v>
       </c>
       <c r="G3" t="n">
-        <v>1.247</v>
+        <v>1.218</v>
       </c>
       <c r="H3" t="n">
         <v>1.194</v>
       </c>
       <c r="I3" t="n">
-        <v>0.794</v>
+        <v>0.779</v>
       </c>
       <c r="J3" t="n">
         <v>0.721</v>
       </c>
       <c r="K3" t="n">
-        <v>0.583</v>
+        <v>0.576</v>
       </c>
       <c r="L3" t="n">
         <v>0.46</v>
       </c>
       <c r="M3" t="n">
-        <v>0.406</v>
+        <v>0.416</v>
       </c>
     </row>
     <row r="4">
@@ -678,25 +678,25 @@
         <v>6.006</v>
       </c>
       <c r="G4" t="n">
-        <v>1.289</v>
+        <v>1.311</v>
       </c>
       <c r="H4" t="n">
         <v>1.267</v>
       </c>
       <c r="I4" t="n">
-        <v>0.834</v>
+        <v>0.847</v>
       </c>
       <c r="J4" t="n">
         <v>0.808</v>
       </c>
       <c r="K4" t="n">
-        <v>0.624</v>
+        <v>0.608</v>
       </c>
       <c r="L4" t="n">
         <v>0.334</v>
       </c>
       <c r="M4" t="n">
-        <v>0.439</v>
+        <v>0.432</v>
       </c>
     </row>
     <row r="5">
@@ -719,25 +719,25 @@
         <v>5.935</v>
       </c>
       <c r="G5" t="n">
-        <v>1.484</v>
+        <v>1.446</v>
       </c>
       <c r="H5" t="n">
         <v>0.785</v>
       </c>
       <c r="I5" t="n">
-        <v>0.921</v>
+        <v>0.934</v>
       </c>
       <c r="J5" t="n">
         <v>0.73</v>
       </c>
       <c r="K5" t="n">
-        <v>0.69</v>
+        <v>0.678</v>
       </c>
       <c r="L5" t="n">
         <v>0.418</v>
       </c>
       <c r="M5" t="n">
-        <v>0.486</v>
+        <v>0.469</v>
       </c>
     </row>
     <row r="6">
@@ -760,25 +760,25 @@
         <v>6.396</v>
       </c>
       <c r="G6" t="n">
-        <v>1.265</v>
+        <v>1.239</v>
       </c>
       <c r="H6" t="n">
         <v>1.442</v>
       </c>
       <c r="I6" t="n">
-        <v>0.813</v>
+        <v>0.804</v>
       </c>
       <c r="J6" t="n">
         <v>0.363</v>
       </c>
       <c r="K6" t="n">
-        <v>0.596</v>
+        <v>0.595</v>
       </c>
       <c r="L6" t="n">
         <v>0.346</v>
       </c>
       <c r="M6" t="n">
-        <v>0.424</v>
+        <v>0.418</v>
       </c>
     </row>
     <row r="7">
@@ -801,25 +801,25 @@
         <v>6.087</v>
       </c>
       <c r="G7" t="n">
-        <v>1.294</v>
+        <v>1.286</v>
       </c>
       <c r="H7" t="n">
         <v>1.02</v>
       </c>
       <c r="I7" t="n">
-        <v>0.813</v>
+        <v>0.815</v>
       </c>
       <c r="J7" t="n">
         <v>0.806</v>
       </c>
       <c r="K7" t="n">
-        <v>0.603</v>
+        <v>0.607</v>
       </c>
       <c r="L7" t="n">
         <v>0.308</v>
       </c>
       <c r="M7" t="n">
-        <v>0.429</v>
+        <v>0.425</v>
       </c>
     </row>
   </sheetData>
@@ -864,25 +864,25 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9782</v>
+        <v>0.298</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1227</v>
+        <v>0.7193</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2686</v>
+        <v>-0.1424</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0632</v>
+        <v>0.044</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8551</v>
+        <v>0.6755</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1449</v>
+        <v>0.3245</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1925</v>
+        <v>1.4307</v>
       </c>
     </row>
     <row r="3">
@@ -890,25 +890,25 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9328</v>
+        <v>-0.2224</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.1715</v>
+        <v>0.9639</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0078</v>
+        <v>-0.074</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1443</v>
+        <v>0.3514</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7467</v>
+        <v>0.8001</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2533</v>
+        <v>0.1999</v>
       </c>
       <c r="H3" t="n">
-        <v>1.117</v>
+        <v>1.3924</v>
       </c>
     </row>
     <row r="4">
@@ -916,25 +916,25 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.298</v>
+        <v>-0.1558</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7193</v>
+        <v>0.4984</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1424</v>
+        <v>0.4338</v>
       </c>
       <c r="E4" t="n">
-        <v>0.044</v>
+        <v>-0.0551</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6755</v>
+        <v>0.5306</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3245</v>
+        <v>0.4694</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4307</v>
+        <v>2.2023</v>
       </c>
     </row>
     <row r="5">
@@ -942,25 +942,25 @@
         <v>44</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.0317</v>
+        <v>0.5118</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3804</v>
+        <v>0.0451</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4653</v>
+        <v>0.1522</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0255</v>
+        <v>0.2633</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4868</v>
+        <v>0.4104</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5132</v>
+        <v>0.5896</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9416</v>
+        <v>1.7181</v>
       </c>
     </row>
     <row r="6">
@@ -968,25 +968,25 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9529</v>
+        <v>0.9782</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.1546</v>
+        <v>0.1227</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1583</v>
+        <v>-0.2686</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1069</v>
+        <v>0.0632</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9387</v>
+        <v>0.8551</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0613</v>
+        <v>0.1449</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1356</v>
+        <v>1.1925</v>
       </c>
     </row>
     <row r="7">
@@ -994,25 +994,25 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.2224</v>
+        <v>0.9328</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9639</v>
+        <v>-0.1715</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.074</v>
+        <v>-0.0078</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3514</v>
+        <v>0.1443</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8001</v>
+        <v>0.7467</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1999</v>
+        <v>0.2533</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3924</v>
+        <v>1.117</v>
       </c>
     </row>
     <row r="8">
@@ -1020,25 +1020,25 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.1558</v>
+        <v>0.9529</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4984</v>
+        <v>-0.1546</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4338</v>
+        <v>0.1583</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0551</v>
+        <v>0.1069</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5306</v>
+        <v>0.9387</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4694</v>
+        <v>0.0613</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2023</v>
+        <v>1.1356</v>
       </c>
     </row>
     <row r="9">
@@ -1046,25 +1046,25 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5118</v>
+        <v>-0.0657</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0451</v>
+        <v>0.1145</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1522</v>
+        <v>0.7142</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2633</v>
+        <v>-0.0099</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4104</v>
+        <v>0.5486</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5896</v>
+        <v>0.4514</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7181</v>
+        <v>1.0692</v>
       </c>
     </row>
     <row r="10">
@@ -1072,25 +1072,25 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.304</v>
+        <v>0.0542</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2524</v>
+        <v>-0.2507</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0897</v>
+        <v>0.7619</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5952</v>
+        <v>0.0806</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5285</v>
+        <v>0.503</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4715</v>
+        <v>0.497</v>
       </c>
       <c r="H10" t="n">
-        <v>1.9453</v>
+        <v>1.2497</v>
       </c>
     </row>
     <row r="11">
@@ -1098,25 +1098,25 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.0657</v>
+        <v>0.4503</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1145</v>
+        <v>-0.0737</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7142</v>
+        <v>0.2271</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0099</v>
+        <v>-0.4163</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5486</v>
+        <v>0.5526</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4514</v>
+        <v>0.4474</v>
       </c>
       <c r="H11" t="n">
-        <v>1.0692</v>
+        <v>2.5402</v>
       </c>
     </row>
     <row r="12">
@@ -1124,25 +1124,25 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0542</v>
+        <v>0.5228</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.2507</v>
+        <v>0.3466</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7619</v>
+        <v>-0.0777</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0806</v>
+        <v>-0.2078</v>
       </c>
       <c r="F12" t="n">
-        <v>0.503</v>
+        <v>0.5839</v>
       </c>
       <c r="G12" t="n">
-        <v>0.497</v>
+        <v>0.4161</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2497</v>
+        <v>2.1524</v>
       </c>
     </row>
     <row r="13">
@@ -1150,25 +1150,25 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4503</v>
+        <v>-0.0317</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.0737</v>
+        <v>0.3804</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2271</v>
+        <v>0.4653</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.4163</v>
+        <v>0.0255</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5526</v>
+        <v>0.4868</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4474</v>
+        <v>0.5132</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5402</v>
+        <v>1.9416</v>
       </c>
     </row>
     <row r="14">
@@ -1176,25 +1176,25 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.5228</v>
+        <v>0.304</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3466</v>
+        <v>0.2524</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0777</v>
+        <v>0.0897</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2078</v>
+        <v>0.5952</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5839</v>
+        <v>0.5285</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4161</v>
+        <v>0.4715</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1524</v>
+        <v>1.9453</v>
       </c>
     </row>
   </sheetData>
@@ -1230,13 +1230,13 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7516</v>
+        <v>0.7587</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5649</v>
+        <v>0.5756</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4351</v>
+        <v>0.4244</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -1247,13 +1247,13 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7155</v>
+        <v>0.6728</v>
       </c>
       <c r="C3" t="n">
-        <v>0.512</v>
+        <v>0.4527</v>
       </c>
       <c r="D3" t="n">
-        <v>0.488</v>
+        <v>0.5473</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -1264,13 +1264,13 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7587</v>
+        <v>0.4992</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5756</v>
+        <v>0.2492</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4244</v>
+        <v>0.7508</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -1281,13 +1281,13 @@
         <v>44</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5133</v>
+        <v>0.684</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2635</v>
+        <v>0.4679</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7365</v>
+        <v>0.5321</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -1298,13 +1298,13 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.6911</v>
+        <v>0.7516</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4777</v>
+        <v>0.5649</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5223</v>
+        <v>0.4351</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -1315,13 +1315,13 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.6728</v>
+        <v>0.7155</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4527</v>
+        <v>0.512</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5473</v>
+        <v>0.488</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -1332,13 +1332,13 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.4992</v>
+        <v>0.6911</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2492</v>
+        <v>0.4777</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7508</v>
+        <v>0.5223</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -1349,13 +1349,13 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.684</v>
+        <v>0.5393</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4679</v>
+        <v>0.2909</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5321</v>
+        <v>0.7091</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -1366,13 +1366,13 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7038</v>
+        <v>0.5412</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4954</v>
+        <v>0.2928</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5046</v>
+        <v>0.7072</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -1383,13 +1383,13 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5393</v>
+        <v>0.7187</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2909</v>
+        <v>0.5166</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7091</v>
+        <v>0.4834</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -1400,13 +1400,13 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.5412</v>
+        <v>0.7192</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2928</v>
+        <v>0.5172</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7072</v>
+        <v>0.4828</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -1417,13 +1417,13 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.7187</v>
+        <v>0.5133</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5166</v>
+        <v>0.2635</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4834</v>
+        <v>0.7365</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -1434,13 +1434,13 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.7192</v>
+        <v>0.7038</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5172</v>
+        <v>0.4954</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4828</v>
+        <v>0.5046</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -1482,19 +1482,19 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7094</v>
+        <v>0.7468</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0822</v>
+        <v>0.0467</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5841</v>
+        <v>0.6042</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4159</v>
+        <v>0.3958</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0269</v>
+        <v>1.0078</v>
       </c>
     </row>
     <row r="3">
@@ -1502,19 +1502,19 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8531</v>
+        <v>0.9028</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.132</v>
+        <v>-0.2432</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6021</v>
+        <v>0.5953</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3979</v>
+        <v>0.4047</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0479</v>
+        <v>1.1444</v>
       </c>
     </row>
     <row r="4">
@@ -1522,19 +1522,19 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7468</v>
+        <v>-0.0423</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0467</v>
+        <v>0.6623</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6042</v>
+        <v>0.4048</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3958</v>
+        <v>0.5952</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0078</v>
+        <v>1.0082</v>
       </c>
     </row>
     <row r="5">
@@ -1542,19 +1542,19 @@
         <v>44</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5282</v>
+        <v>0.2901</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0044</v>
+        <v>0.4956</v>
       </c>
       <c r="D5" t="n">
-        <v>0.282</v>
+        <v>0.5123</v>
       </c>
       <c r="E5" t="n">
-        <v>0.718</v>
+        <v>0.4877</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0001</v>
+        <v>1.6132</v>
       </c>
     </row>
     <row r="6">
@@ -1562,19 +1562,19 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.6447</v>
+        <v>0.7094</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0847</v>
+        <v>0.0822</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4921</v>
+        <v>0.5841</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5079</v>
+        <v>0.4159</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0345</v>
+        <v>1.0269</v>
       </c>
     </row>
     <row r="7">
@@ -1582,19 +1582,19 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.9028</v>
+        <v>0.8531</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.2432</v>
+        <v>-0.132</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5953</v>
+        <v>0.6021</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4047</v>
+        <v>0.3979</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1444</v>
+        <v>1.0479</v>
       </c>
     </row>
     <row r="8">
@@ -1602,19 +1602,19 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.0423</v>
+        <v>0.6447</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6623</v>
+        <v>0.0847</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4048</v>
+        <v>0.4921</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5952</v>
+        <v>0.5079</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0082</v>
+        <v>1.0345</v>
       </c>
     </row>
     <row r="9">
@@ -1622,19 +1622,19 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2901</v>
+        <v>-0.203</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4956</v>
+        <v>0.9016</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5123</v>
+        <v>0.6217</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4877</v>
+        <v>0.3783</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6132</v>
+        <v>1.1011</v>
       </c>
     </row>
     <row r="10">
@@ -1642,19 +1642,19 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.627</v>
+        <v>0.0093</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1212</v>
+        <v>0.6526</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5043</v>
+        <v>0.4337</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4957</v>
+        <v>0.5663</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0746</v>
+        <v>1.0004</v>
       </c>
     </row>
     <row r="11">
@@ -1662,19 +1662,19 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.203</v>
+        <v>0.6238</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9016</v>
+        <v>0.1432</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6217</v>
+        <v>0.5231</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3783</v>
+        <v>0.4769</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1011</v>
+        <v>1.1051</v>
       </c>
     </row>
     <row r="12">
@@ -1682,19 +1682,19 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0093</v>
+        <v>0.3565</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6526</v>
+        <v>0.4601</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4337</v>
+        <v>0.5471</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5663</v>
+        <v>0.4529</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0004</v>
+        <v>1.8825</v>
       </c>
     </row>
     <row r="13">
@@ -1702,19 +1702,19 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.6238</v>
+        <v>0.5282</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1432</v>
+        <v>0.0044</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5231</v>
+        <v>0.282</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4769</v>
+        <v>0.718</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1051</v>
+        <v>1.0001</v>
       </c>
     </row>
     <row r="14">
@@ -1722,19 +1722,19 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3565</v>
+        <v>0.627</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4601</v>
+        <v>0.1212</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5471</v>
+        <v>0.5043</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4529</v>
+        <v>0.4957</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8825</v>
+        <v>1.0746</v>
       </c>
     </row>
   </sheetData>
@@ -1776,22 +1776,22 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7232</v>
+        <v>0.6396</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0278</v>
+        <v>0.0182</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0583</v>
+        <v>0.2062</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5952</v>
+        <v>0.6045</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4048</v>
+        <v>0.3955</v>
       </c>
       <c r="G2" t="n">
-        <v>1.016</v>
+        <v>1.2074</v>
       </c>
     </row>
     <row r="3">
@@ -1799,22 +1799,22 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9136</v>
+        <v>0.5895</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.1941</v>
+        <v>-0.2209</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0245</v>
+        <v>0.4266</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6484</v>
+        <v>0.6258</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3516</v>
+        <v>0.3742</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0916</v>
+        <v>2.1402</v>
       </c>
     </row>
     <row r="4">
@@ -1822,22 +1822,22 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6396</v>
+        <v>0.0111</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0182</v>
+        <v>0.6165</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2062</v>
+        <v>0.0437</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6045</v>
+        <v>0.4084</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3955</v>
+        <v>0.5916</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2074</v>
+        <v>1.0107</v>
       </c>
     </row>
     <row r="5">
@@ -1845,22 +1845,22 @@
         <v>44</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.0259</v>
+        <v>0.606</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0901</v>
+        <v>0.38</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7369</v>
+        <v>-0.2833</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5736</v>
+        <v>0.6078</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4264</v>
+        <v>0.3922</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0324</v>
+        <v>2.1607</v>
       </c>
     </row>
     <row r="6">
@@ -1868,22 +1868,22 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7719</v>
+        <v>0.7232</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0097</v>
+        <v>0.0278</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0882</v>
+        <v>0.0583</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5412</v>
+        <v>0.5952</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4588</v>
+        <v>0.4048</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0265</v>
+        <v>1.016</v>
       </c>
     </row>
     <row r="7">
@@ -1891,22 +1891,22 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.5895</v>
+        <v>0.9136</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.2209</v>
+        <v>-0.1941</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4266</v>
+        <v>-0.0245</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6258</v>
+        <v>0.6484</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3742</v>
+        <v>0.3516</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1402</v>
+        <v>1.0916</v>
       </c>
     </row>
     <row r="8">
@@ -1914,22 +1914,22 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0111</v>
+        <v>0.7719</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6165</v>
+        <v>0.0097</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0437</v>
+        <v>-0.0882</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4084</v>
+        <v>0.5412</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5916</v>
+        <v>0.4588</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0107</v>
+        <v>1.0265</v>
       </c>
     </row>
     <row r="9">
@@ -1937,22 +1937,22 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.606</v>
+        <v>-0.0513</v>
       </c>
       <c r="C9" t="n">
-        <v>0.38</v>
+        <v>0.8316</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2833</v>
+        <v>-0.0515</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6078</v>
+        <v>0.6219</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3922</v>
+        <v>0.3781</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1607</v>
+        <v>1.0153</v>
       </c>
     </row>
     <row r="10">
@@ -1960,22 +1960,22 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4977</v>
+        <v>-0.1524</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1012</v>
+        <v>0.6508</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2362</v>
+        <v>0.3146</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5096</v>
+        <v>0.5181</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4904</v>
+        <v>0.4819</v>
       </c>
       <c r="G10" t="n">
-        <v>1.5243</v>
+        <v>1.5699</v>
       </c>
     </row>
     <row r="11">
@@ -1983,22 +1983,22 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.0513</v>
+        <v>0.4951</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8316</v>
+        <v>0.1221</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0515</v>
+        <v>0.239</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6219</v>
+        <v>0.529</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3781</v>
+        <v>0.471</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0153</v>
+        <v>1.5823</v>
       </c>
     </row>
     <row r="12">
@@ -2006,22 +2006,22 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.1524</v>
+        <v>0.5214</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6508</v>
+        <v>0.375</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3146</v>
+        <v>-0.0956</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5181</v>
+        <v>0.5717</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4819</v>
+        <v>0.4283</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5699</v>
+        <v>1.8958</v>
       </c>
     </row>
     <row r="13">
@@ -2029,22 +2029,22 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4951</v>
+        <v>-0.0259</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1221</v>
+        <v>0.0901</v>
       </c>
       <c r="D13" t="n">
-        <v>0.239</v>
+        <v>0.7369</v>
       </c>
       <c r="E13" t="n">
-        <v>0.529</v>
+        <v>0.5736</v>
       </c>
       <c r="F13" t="n">
-        <v>0.471</v>
+        <v>0.4264</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5823</v>
+        <v>1.0324</v>
       </c>
     </row>
     <row r="14">
@@ -2052,22 +2052,22 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.5214</v>
+        <v>0.4977</v>
       </c>
       <c r="C14" t="n">
-        <v>0.375</v>
+        <v>0.1012</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0956</v>
+        <v>0.2362</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5717</v>
+        <v>0.5096</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4283</v>
+        <v>0.4904</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8958</v>
+        <v>1.5243</v>
       </c>
     </row>
   </sheetData>
@@ -2103,13 +2103,13 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5955</v>
+        <v>0.5671</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3546</v>
+        <v>0.3216</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6454</v>
+        <v>0.6784</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -2120,13 +2120,13 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7151</v>
+        <v>0.4631</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5113</v>
+        <v>0.2145</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4887</v>
+        <v>0.7855</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -2137,13 +2137,13 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5671</v>
+        <v>0.8109</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3216</v>
+        <v>0.6575</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6784</v>
+        <v>0.3425</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -2154,13 +2154,13 @@
         <v>44</v>
       </c>
       <c r="B5" t="n">
-        <v>0.646</v>
+        <v>0.6732</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4174</v>
+        <v>0.4532</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5826</v>
+        <v>0.5468</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -2171,13 +2171,13 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7386</v>
+        <v>0.5955</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5456</v>
+        <v>0.3546</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4544</v>
+        <v>0.6454</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -2188,13 +2188,13 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4631</v>
+        <v>0.7151</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2145</v>
+        <v>0.5113</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7855</v>
+        <v>0.4887</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -2205,13 +2205,13 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.8109</v>
+        <v>0.7386</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6575</v>
+        <v>0.5456</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3425</v>
+        <v>0.4544</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -2222,13 +2222,13 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.6732</v>
+        <v>0.6566</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4532</v>
+        <v>0.4312</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5468</v>
+        <v>0.5688</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -2239,13 +2239,13 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4939</v>
+        <v>0.7479</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2439</v>
+        <v>0.5593</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7561</v>
+        <v>0.4407</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -2256,13 +2256,13 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6566</v>
+        <v>0.6312</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4312</v>
+        <v>0.3985</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5688</v>
+        <v>0.6015</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -2273,13 +2273,13 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.7479</v>
+        <v>0.6947</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5593</v>
+        <v>0.4826</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4407</v>
+        <v>0.5174</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -2290,13 +2290,13 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.6312</v>
+        <v>0.646</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3985</v>
+        <v>0.4174</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6015</v>
+        <v>0.5826</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -2307,13 +2307,13 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6947</v>
+        <v>0.4939</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4826</v>
+        <v>0.2439</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5174</v>
+        <v>0.7561</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -2355,19 +2355,19 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4165</v>
+        <v>0.1725</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2127</v>
+        <v>0.4413</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3549</v>
+        <v>0.3416</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6451</v>
+        <v>0.6584</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4883</v>
+        <v>1.2987</v>
       </c>
     </row>
     <row r="3">
@@ -2375,19 +2375,19 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2219</v>
+        <v>0.0345</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5519</v>
+        <v>0.4739</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5421</v>
+        <v>0.2509</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4579</v>
+        <v>0.7491</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3149</v>
+        <v>1.0106</v>
       </c>
     </row>
     <row r="4">
@@ -2395,19 +2395,19 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1725</v>
+        <v>1.0523</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4413</v>
+        <v>-0.2273</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3416</v>
+        <v>0.7913</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6584</v>
+        <v>0.2087</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2987</v>
+        <v>1.0931</v>
       </c>
     </row>
     <row r="5">
@@ -2415,19 +2415,19 @@
         <v>44</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5662</v>
+        <v>0.6481</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1089</v>
+        <v>0.0516</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4272</v>
+        <v>0.4741</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5728</v>
+        <v>0.5259</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0739</v>
+        <v>1.0127</v>
       </c>
     </row>
     <row r="6">
@@ -2435,19 +2435,19 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1609</v>
+        <v>0.4165</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6428</v>
+        <v>0.2127</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5981</v>
+        <v>0.3549</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4019</v>
+        <v>0.6451</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1249</v>
+        <v>1.4883</v>
       </c>
     </row>
     <row r="7">
@@ -2455,19 +2455,19 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0345</v>
+        <v>0.2219</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4739</v>
+        <v>0.5519</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2509</v>
+        <v>0.5421</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7491</v>
+        <v>0.4579</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0106</v>
+        <v>1.3149</v>
       </c>
     </row>
     <row r="8">
@@ -2475,19 +2475,19 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>1.0523</v>
+        <v>0.1609</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2273</v>
+        <v>0.6428</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7913</v>
+        <v>0.5981</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2087</v>
+        <v>0.4019</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0931</v>
+        <v>1.1249</v>
       </c>
     </row>
     <row r="9">
@@ -2495,19 +2495,19 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.6481</v>
+        <v>0.6584</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0516</v>
+        <v>0.0223</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4741</v>
+        <v>0.4566</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5259</v>
+        <v>0.5434</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0127</v>
+        <v>1.0023</v>
       </c>
     </row>
     <row r="10">
@@ -2515,19 +2515,19 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.1848</v>
+        <v>0.6545</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7414</v>
+        <v>0.1271</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3732</v>
+        <v>0.5724</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6268</v>
+        <v>0.4276</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1238</v>
+        <v>1.0753</v>
       </c>
     </row>
     <row r="11">
@@ -2535,19 +2535,19 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6584</v>
+        <v>0.581</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0223</v>
+        <v>0.0768</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4566</v>
+        <v>0.4121</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5434</v>
+        <v>0.5879</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0023</v>
+        <v>1.035</v>
       </c>
     </row>
     <row r="12">
@@ -2555,19 +2555,19 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.6545</v>
+        <v>0.2704</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1271</v>
+        <v>0.4778</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5724</v>
+        <v>0.5</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4276</v>
+        <v>0.5</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0753</v>
+        <v>1.5808</v>
       </c>
     </row>
     <row r="13">
@@ -2575,19 +2575,19 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.581</v>
+        <v>0.5662</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0768</v>
+        <v>0.1089</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4121</v>
+        <v>0.4272</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5879</v>
+        <v>0.5728</v>
       </c>
       <c r="F13" t="n">
-        <v>1.035</v>
+        <v>1.0739</v>
       </c>
     </row>
     <row r="14">
@@ -2595,19 +2595,19 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.2704</v>
+        <v>-0.1848</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4778</v>
+        <v>0.7414</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5</v>
+        <v>0.3732</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5</v>
+        <v>0.6268</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5808</v>
+        <v>1.1238</v>
       </c>
     </row>
   </sheetData>
@@ -2649,22 +2649,22 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2659</v>
+        <v>0.1744</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3913</v>
+        <v>-0.0273</v>
       </c>
       <c r="D2" t="n">
-        <v>0.011</v>
+        <v>0.553</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3727</v>
+        <v>0.4215</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6273</v>
+        <v>0.5785</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7631</v>
+        <v>1.2023</v>
       </c>
     </row>
     <row r="3">
@@ -2672,22 +2672,22 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1297</v>
+        <v>0.058</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3444</v>
+        <v>-0.022</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3729</v>
+        <v>0.5483</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5443</v>
+        <v>0.3243</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4557</v>
+        <v>0.6757</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2364</v>
+        <v>1.0256</v>
       </c>
     </row>
     <row r="4">
@@ -2695,22 +2695,22 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1744</v>
+        <v>0.9158</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.0273</v>
+        <v>-0.1518</v>
       </c>
       <c r="D4" t="n">
-        <v>0.553</v>
+        <v>0.1524</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4215</v>
+        <v>0.8277</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5785</v>
+        <v>0.1723</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2023</v>
+        <v>1.1116</v>
       </c>
     </row>
     <row r="5">
@@ -2718,22 +2718,22 @@
         <v>44</v>
       </c>
       <c r="B5" t="n">
-        <v>0.3763</v>
+        <v>0.5629</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4356</v>
+        <v>-0.0506</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1016</v>
+        <v>0.2681</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4661</v>
+        <v>0.5074</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5339</v>
+        <v>0.4926</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0785</v>
+        <v>1.4503</v>
       </c>
     </row>
     <row r="6">
@@ -2741,22 +2741,22 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0758</v>
+        <v>0.2659</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3723</v>
+        <v>0.3913</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4333</v>
+        <v>0.011</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6019</v>
+        <v>0.3727</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3981</v>
+        <v>0.6273</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0238</v>
+        <v>1.7631</v>
       </c>
     </row>
     <row r="7">
@@ -2764,22 +2764,22 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.058</v>
+        <v>0.1297</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.022</v>
+        <v>0.3444</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5483</v>
+        <v>0.3729</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3243</v>
+        <v>0.5443</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6757</v>
+        <v>0.4557</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0256</v>
+        <v>2.2364</v>
       </c>
     </row>
     <row r="8">
@@ -2787,22 +2787,22 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.9158</v>
+        <v>0.0758</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.1518</v>
+        <v>0.3723</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1524</v>
+        <v>0.4333</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8277</v>
+        <v>0.6019</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1723</v>
+        <v>0.3981</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1116</v>
+        <v>2.0238</v>
       </c>
     </row>
     <row r="9">
@@ -2810,22 +2810,22 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5629</v>
+        <v>0.5325</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.0506</v>
+        <v>0.1019</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2681</v>
+        <v>0.1096</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5074</v>
+        <v>0.4587</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4926</v>
+        <v>0.5413</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4503</v>
+        <v>1.1606</v>
       </c>
     </row>
     <row r="10">
@@ -2833,22 +2833,22 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.2641</v>
+        <v>0.4834</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5846</v>
+        <v>0.3083</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2721</v>
+        <v>0.0491</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3879</v>
+        <v>0.5771</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6121</v>
+        <v>0.4229</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8543</v>
+        <v>1.723</v>
       </c>
     </row>
     <row r="11">
@@ -2856,22 +2856,22 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5325</v>
+        <v>0.3606</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1019</v>
+        <v>0.5434</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1096</v>
+        <v>-0.2242</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4587</v>
+        <v>0.5013</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5413</v>
+        <v>0.4987</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1606</v>
+        <v>2.1212</v>
       </c>
     </row>
     <row r="12">
@@ -2879,22 +2879,22 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4834</v>
+        <v>0.0893</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3083</v>
+        <v>0.6589</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0491</v>
+        <v>0.0379</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5771</v>
+        <v>0.5569</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4229</v>
+        <v>0.4431</v>
       </c>
       <c r="G12" t="n">
-        <v>1.723</v>
+        <v>1.0435</v>
       </c>
     </row>
     <row r="13">
@@ -2902,22 +2902,22 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.3606</v>
+        <v>0.3763</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5434</v>
+        <v>0.4356</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2242</v>
+        <v>-0.1016</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5013</v>
+        <v>0.4661</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4987</v>
+        <v>0.5339</v>
       </c>
       <c r="G13" t="n">
-        <v>2.1212</v>
+        <v>2.0785</v>
       </c>
     </row>
     <row r="14">
@@ -2925,22 +2925,22 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0893</v>
+        <v>-0.2641</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6589</v>
+        <v>0.5846</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0379</v>
+        <v>0.2721</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5569</v>
+        <v>0.3879</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4431</v>
+        <v>0.6121</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0435</v>
+        <v>1.8543</v>
       </c>
     </row>
   </sheetData>
@@ -2985,25 +2985,25 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2061</v>
+        <v>0.0928</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0014</v>
+        <v>0.5528</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0455</v>
+        <v>0.0287</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5073</v>
+        <v>0.0312</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4088</v>
+        <v>0.4216</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5912</v>
+        <v>0.5784</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3396</v>
+        <v>1.0685</v>
       </c>
     </row>
     <row r="3">
@@ -3011,25 +3011,25 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0687</v>
+        <v>0.0008</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3475</v>
+        <v>0.5396</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1176</v>
+        <v>0.0999</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3317</v>
+        <v>-0.0434</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5542</v>
+        <v>0.3258</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4458</v>
+        <v>0.6742</v>
       </c>
       <c r="H3" t="n">
-        <v>2.311</v>
+        <v>1.0818</v>
       </c>
     </row>
     <row r="4">
@@ -3037,25 +3037,25 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0928</v>
+        <v>0.9332</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5528</v>
+        <v>0.2274</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0287</v>
+        <v>-0.1565</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0312</v>
+        <v>-0.1245</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4216</v>
+        <v>0.833</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5784</v>
+        <v>0.167</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0685</v>
+        <v>1.2161</v>
       </c>
     </row>
     <row r="5">
@@ -3063,25 +3063,25 @@
         <v>44</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5037</v>
+        <v>0.55</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1007</v>
+        <v>0.3064</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2458</v>
+        <v>-0.0549</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0732</v>
+        <v>-0.0374</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4672</v>
+        <v>0.5088</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5328</v>
+        <v>0.4912</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5945</v>
+        <v>1.6011</v>
       </c>
     </row>
     <row r="6">
@@ -3089,25 +3089,25 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0068</v>
+        <v>0.2061</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4003</v>
+        <v>0.0014</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1483</v>
+        <v>-0.0455</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3496</v>
+        <v>0.5073</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6126</v>
+        <v>0.4088</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3874</v>
+        <v>0.5912</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2561</v>
+        <v>1.3396</v>
       </c>
     </row>
     <row r="7">
@@ -3115,25 +3115,25 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0008</v>
+        <v>0.0687</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5396</v>
+        <v>0.3475</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0999</v>
+        <v>0.1176</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0434</v>
+        <v>0.3317</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3258</v>
+        <v>0.5542</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6742</v>
+        <v>0.4458</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0818</v>
+        <v>2.311</v>
       </c>
     </row>
     <row r="8">
@@ -3141,25 +3141,25 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.9332</v>
+        <v>0.0068</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2274</v>
+        <v>0.4003</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1565</v>
+        <v>0.1483</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1245</v>
+        <v>0.3496</v>
       </c>
       <c r="F8" t="n">
-        <v>0.833</v>
+        <v>0.6126</v>
       </c>
       <c r="G8" t="n">
-        <v>0.167</v>
+        <v>0.3874</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2161</v>
+        <v>2.2561</v>
       </c>
     </row>
     <row r="9">
@@ -3167,25 +3167,25 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.55</v>
+        <v>0.5721</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3064</v>
+        <v>0.1395</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0549</v>
+        <v>0.0314</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0374</v>
+        <v>-0.0084</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5088</v>
+        <v>0.4602</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4912</v>
+        <v>0.5398</v>
       </c>
       <c r="H9" t="n">
-        <v>1.6011</v>
+        <v>1.1252</v>
       </c>
     </row>
     <row r="10">
@@ -3193,25 +3193,25 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.0963</v>
+        <v>0.4999</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2061</v>
+        <v>0.0616</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6646</v>
+        <v>0.0382</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.119</v>
+        <v>0.2382</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4098</v>
+        <v>0.5806</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5902</v>
+        <v>0.4194</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3068</v>
+        <v>1.4811</v>
       </c>
     </row>
     <row r="11">
@@ -3219,25 +3219,25 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5721</v>
+        <v>0.5128</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1395</v>
+        <v>-0.2288</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0314</v>
+        <v>0.2783</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0084</v>
+        <v>0.1322</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4602</v>
+        <v>0.5016</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5398</v>
+        <v>0.4984</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1252</v>
+        <v>2.1522</v>
       </c>
     </row>
     <row r="12">
@@ -3245,25 +3245,25 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4999</v>
+        <v>0.2779</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0616</v>
+        <v>-0.0011</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0382</v>
+        <v>0.5507</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2382</v>
+        <v>0.0031</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5806</v>
+        <v>0.5667</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4194</v>
+        <v>0.4333</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4811</v>
+        <v>1.4783</v>
       </c>
     </row>
     <row r="13">
@@ -3271,25 +3271,25 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5128</v>
+        <v>0.5037</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.2288</v>
+        <v>-0.1007</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2783</v>
+        <v>0.2458</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1322</v>
+        <v>0.0732</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5016</v>
+        <v>0.4672</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4984</v>
+        <v>0.5328</v>
       </c>
       <c r="H13" t="n">
-        <v>2.1522</v>
+        <v>1.5945</v>
       </c>
     </row>
     <row r="14">
@@ -3297,25 +3297,25 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.2779</v>
+        <v>-0.0963</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.0011</v>
+        <v>0.2061</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5507</v>
+        <v>0.6646</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0031</v>
+        <v>-0.119</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5667</v>
+        <v>0.4098</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4333</v>
+        <v>0.5902</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4783</v>
+        <v>1.3068</v>
       </c>
     </row>
   </sheetData>
@@ -3351,13 +3351,13 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6298</v>
+        <v>0.7178</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3966</v>
+        <v>0.5152</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6034</v>
+        <v>0.4848</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3368,13 +3368,13 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7</v>
+        <v>0.7178</v>
       </c>
       <c r="C3" t="n">
-        <v>0.49</v>
+        <v>0.5152</v>
       </c>
       <c r="D3" t="n">
-        <v>0.51</v>
+        <v>0.4848</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3385,13 +3385,13 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7178</v>
+        <v>0.7262</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5152</v>
+        <v>0.5273</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4848</v>
+        <v>0.4727</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -3402,13 +3402,13 @@
         <v>44</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7545</v>
+        <v>0.6763</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5693</v>
+        <v>0.4573</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4307</v>
+        <v>0.5427</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -3419,13 +3419,13 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7592</v>
+        <v>0.6298</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5764</v>
+        <v>0.3966</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4236</v>
+        <v>0.6034</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -3436,13 +3436,13 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7178</v>
+        <v>0.7</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5152</v>
+        <v>0.49</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4848</v>
+        <v>0.51</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -3453,13 +3453,13 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7262</v>
+        <v>0.7592</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5273</v>
+        <v>0.5764</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4727</v>
+        <v>0.4236</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -3470,13 +3470,13 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.6763</v>
+        <v>0.6969</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4573</v>
+        <v>0.4857</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5427</v>
+        <v>0.5143</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -3487,13 +3487,13 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7691</v>
+        <v>0.4721</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5915</v>
+        <v>0.2229</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4085</v>
+        <v>0.7771</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -3504,13 +3504,13 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6969</v>
+        <v>0.6487</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4857</v>
+        <v>0.4208</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5143</v>
+        <v>0.5792</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -3521,13 +3521,13 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4721</v>
+        <v>0.691</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2229</v>
+        <v>0.4774</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7771</v>
+        <v>0.5226</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -3538,13 +3538,13 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.6487</v>
+        <v>0.7545</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4208</v>
+        <v>0.5693</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5792</v>
+        <v>0.4307</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -3555,13 +3555,13 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.691</v>
+        <v>0.7691</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4774</v>
+        <v>0.5915</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5226</v>
+        <v>0.4085</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -3603,19 +3603,19 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8622</v>
+        <v>0.6524</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1807</v>
+        <v>0.1358</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5815</v>
+        <v>0.5546</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4185</v>
+        <v>0.4454</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0877</v>
+        <v>1.0865</v>
       </c>
     </row>
     <row r="3">
@@ -3623,19 +3623,19 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7946</v>
+        <v>0.2036</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0315</v>
+        <v>0.6001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6012</v>
+        <v>0.5542</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3988</v>
+        <v>0.4458</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0031</v>
+        <v>1.2273</v>
       </c>
     </row>
     <row r="4">
@@ -3643,19 +3643,19 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6524</v>
+        <v>0.0256</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1358</v>
+        <v>0.7939</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5546</v>
+        <v>0.6562</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4454</v>
+        <v>0.3438</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0865</v>
+        <v>1.0021</v>
       </c>
     </row>
     <row r="5">
@@ -3663,19 +3663,19 @@
         <v>44</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2811</v>
+        <v>0.1049</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5615</v>
+        <v>0.6553</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5913</v>
+        <v>0.5263</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4087</v>
+        <v>0.4737</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4716</v>
+        <v>1.0513</v>
       </c>
     </row>
     <row r="6">
@@ -3683,19 +3683,19 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>1.0563</v>
+        <v>0.8622</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.2354</v>
+        <v>-0.1807</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8608</v>
+        <v>0.5815</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1392</v>
+        <v>0.4185</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0991</v>
+        <v>1.0877</v>
       </c>
     </row>
     <row r="7">
@@ -3703,19 +3703,19 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2036</v>
+        <v>0.7946</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6001</v>
+        <v>-0.0315</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5542</v>
+        <v>0.6012</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4458</v>
+        <v>0.3988</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2273</v>
+        <v>1.0031</v>
       </c>
     </row>
     <row r="8">
@@ -3723,19 +3723,19 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0256</v>
+        <v>1.0563</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7939</v>
+        <v>-0.2354</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6562</v>
+        <v>0.8608</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3438</v>
+        <v>0.1392</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0021</v>
+        <v>1.0991</v>
       </c>
     </row>
     <row r="9">
@@ -3743,19 +3743,19 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1049</v>
+        <v>-0.0452</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6553</v>
+        <v>0.8341</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5263</v>
+        <v>0.6507</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4737</v>
+        <v>0.3493</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0513</v>
+        <v>1.0059</v>
       </c>
     </row>
     <row r="10">
@@ -3763,19 +3763,19 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4761</v>
+        <v>-0.3351</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3761</v>
+        <v>0.88</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5918</v>
+        <v>0.5185</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4082</v>
+        <v>0.4815</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8982</v>
+        <v>1.284</v>
       </c>
     </row>
     <row r="11">
@@ -3783,19 +3783,19 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.0452</v>
+        <v>0.6231</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8341</v>
+        <v>0.088</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6507</v>
+        <v>0.4644</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3493</v>
+        <v>0.5356</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0059</v>
+        <v>1.0399</v>
       </c>
     </row>
     <row r="12">
@@ -3803,19 +3803,19 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.3351</v>
+        <v>0.4644</v>
       </c>
       <c r="C12" t="n">
-        <v>0.88</v>
+        <v>0.3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5185</v>
+        <v>0.4796</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4815</v>
+        <v>0.5204</v>
       </c>
       <c r="F12" t="n">
-        <v>1.284</v>
+        <v>1.7107</v>
       </c>
     </row>
     <row r="13">
@@ -3823,19 +3823,19 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.6231</v>
+        <v>0.2811</v>
       </c>
       <c r="C13" t="n">
-        <v>0.088</v>
+        <v>0.5615</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4644</v>
+        <v>0.5913</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5356</v>
+        <v>0.4087</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0399</v>
+        <v>1.4716</v>
       </c>
     </row>
     <row r="14">
@@ -3843,19 +3843,19 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.4644</v>
+        <v>0.4761</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3</v>
+        <v>0.3761</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4796</v>
+        <v>0.5918</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5204</v>
+        <v>0.4082</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7107</v>
+        <v>1.8982</v>
       </c>
     </row>
   </sheetData>
@@ -6136,22 +6136,22 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.2596</v>
+        <v>0.0074</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4826</v>
+        <v>0.2408</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5109</v>
+        <v>0.5927</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6134</v>
+        <v>0.6159</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3866</v>
+        <v>0.3841</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4826</v>
+        <v>1.3216</v>
       </c>
     </row>
     <row r="3">
@@ -6159,22 +6159,22 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.034</v>
+        <v>0.4657</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6271</v>
+        <v>-0.0709</v>
       </c>
       <c r="D3" t="n">
-        <v>0.218</v>
+        <v>0.4489</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6016</v>
+        <v>0.5941</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3984</v>
+        <v>0.4059</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2448</v>
+        <v>2.045</v>
       </c>
     </row>
     <row r="4">
@@ -6182,22 +6182,22 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0074</v>
+        <v>0.733</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2408</v>
+        <v>-0.0156</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5927</v>
+        <v>0.1324</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6159</v>
+        <v>0.6563</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3841</v>
+        <v>0.3437</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3216</v>
+        <v>1.0661</v>
       </c>
     </row>
     <row r="5">
@@ -6205,22 +6205,22 @@
         <v>44</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5083</v>
+        <v>0.6368</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1763</v>
+        <v>0.1285</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1963</v>
+        <v>0.0231</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5915</v>
+        <v>0.5318</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4085</v>
+        <v>0.4682</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5541</v>
+        <v>1.0841</v>
       </c>
     </row>
     <row r="6">
@@ -6228,22 +6228,22 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.1028</v>
+        <v>-0.2596</v>
       </c>
       <c r="C6" t="n">
-        <v>1.126</v>
+        <v>0.4826</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1531</v>
+        <v>0.5109</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9561</v>
+        <v>0.6134</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0439</v>
+        <v>0.3866</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0539</v>
+        <v>2.4826</v>
       </c>
     </row>
     <row r="7">
@@ -6251,22 +6251,22 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4657</v>
+        <v>-0.034</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0709</v>
+        <v>0.6271</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4489</v>
+        <v>0.218</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5941</v>
+        <v>0.6016</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4059</v>
+        <v>0.3984</v>
       </c>
       <c r="G7" t="n">
-        <v>2.045</v>
+        <v>1.2448</v>
       </c>
     </row>
     <row r="8">
@@ -6274,22 +6274,22 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.733</v>
+        <v>-0.1028</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0156</v>
+        <v>1.126</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1324</v>
+        <v>-0.1531</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6563</v>
+        <v>0.9561</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3437</v>
+        <v>0.0439</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0661</v>
+        <v>1.0539</v>
       </c>
     </row>
     <row r="9">
@@ -6297,22 +6297,22 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.6368</v>
+        <v>0.7696</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1285</v>
+        <v>-0.0754</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0231</v>
+        <v>0.1221</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5318</v>
+        <v>0.6507</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4682</v>
+        <v>0.3493</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0841</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="10">
@@ -6320,22 +6320,22 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2865</v>
+        <v>0.9021</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2224</v>
+        <v>-0.0991</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3902</v>
+        <v>-0.2525</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6071</v>
+        <v>0.554</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3929</v>
+        <v>0.446</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4884</v>
+        <v>1.1816</v>
       </c>
     </row>
     <row r="11">
@@ -6343,22 +6343,22 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7696</v>
+        <v>0.1265</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0754</v>
+        <v>0.6015</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1221</v>
+        <v>0.0218</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6507</v>
+        <v>0.4811</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3493</v>
+        <v>0.5189</v>
       </c>
       <c r="G11" t="n">
-        <v>1.07</v>
+        <v>1.091</v>
       </c>
     </row>
     <row r="12">
@@ -6366,22 +6366,22 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.9021</v>
+        <v>0.3179</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.0991</v>
+        <v>0.4546</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2525</v>
+        <v>0.0287</v>
       </c>
       <c r="E12" t="n">
-        <v>0.554</v>
+        <v>0.4921</v>
       </c>
       <c r="F12" t="n">
-        <v>0.446</v>
+        <v>0.5079</v>
       </c>
       <c r="G12" t="n">
-        <v>1.1816</v>
+        <v>1.7989</v>
       </c>
     </row>
     <row r="13">
@@ -6389,22 +6389,22 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1265</v>
+        <v>0.5083</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6015</v>
+        <v>0.1763</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0218</v>
+        <v>0.1963</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4811</v>
+        <v>0.5915</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5189</v>
+        <v>0.4085</v>
       </c>
       <c r="G13" t="n">
-        <v>1.091</v>
+        <v>1.5541</v>
       </c>
     </row>
     <row r="14">
@@ -6412,22 +6412,22 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3179</v>
+        <v>0.2865</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4546</v>
+        <v>0.2224</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0287</v>
+        <v>0.3902</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4921</v>
+        <v>0.6071</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5079</v>
+        <v>0.3929</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7989</v>
+        <v>2.4884</v>
       </c>
     </row>
   </sheetData>
@@ -6472,25 +6472,25 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1039</v>
+        <v>-0.0148</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7835</v>
+        <v>0.4396</v>
       </c>
       <c r="D2" t="n">
-        <v>0.288</v>
+        <v>0.475</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1853</v>
+        <v>-0.0159</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6498</v>
+        <v>0.6165</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3502</v>
+        <v>0.3835</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4298</v>
+        <v>1.9926</v>
       </c>
     </row>
     <row r="3">
@@ -6498,25 +6498,25 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0149</v>
+        <v>0.2851</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6218</v>
+        <v>-0.0307</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0848</v>
+        <v>0.4845</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1327</v>
+        <v>0.1344</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6046</v>
+        <v>0.6056</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3954</v>
+        <v>0.3944</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1308</v>
+        <v>1.8094</v>
       </c>
     </row>
     <row r="4">
@@ -6524,25 +6524,25 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.0148</v>
+        <v>0.6045</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4396</v>
+        <v>-0.0661</v>
       </c>
       <c r="D4" t="n">
-        <v>0.475</v>
+        <v>0.2066</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0159</v>
+        <v>0.1313</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6165</v>
+        <v>0.6573</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3835</v>
+        <v>0.3427</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9926</v>
+        <v>1.3609</v>
       </c>
     </row>
     <row r="5">
@@ -6550,25 +6550,25 @@
         <v>44</v>
       </c>
       <c r="B5" t="n">
-        <v>0.4857</v>
+        <v>0.7182</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2251</v>
+        <v>0.2436</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1798</v>
+        <v>0.0037</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0261</v>
+        <v>-0.1443</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5959</v>
+        <v>0.5735</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4041</v>
+        <v>0.4265</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7233</v>
+        <v>1.3154</v>
       </c>
     </row>
     <row r="6">
@@ -6576,25 +6576,25 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0409</v>
+        <v>-0.1039</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9154</v>
+        <v>0.7835</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3274</v>
+        <v>0.288</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2897</v>
+        <v>-0.1853</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9677</v>
+        <v>0.6498</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0323</v>
+        <v>0.3502</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4742</v>
+        <v>1.4298</v>
       </c>
     </row>
     <row r="7">
@@ -6602,25 +6602,25 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2851</v>
+        <v>0.0149</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0307</v>
+        <v>0.6218</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4845</v>
+        <v>0.0848</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1344</v>
+        <v>0.1327</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6056</v>
+        <v>0.6046</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3944</v>
+        <v>0.3954</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8094</v>
+        <v>1.1308</v>
       </c>
     </row>
     <row r="8">
@@ -6628,25 +6628,25 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.6045</v>
+        <v>0.0409</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0661</v>
+        <v>0.9154</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2066</v>
+        <v>-0.3274</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1313</v>
+        <v>0.2897</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6573</v>
+        <v>0.9677</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3427</v>
+        <v>0.0323</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3609</v>
+        <v>1.4742</v>
       </c>
     </row>
     <row r="9">
@@ -6654,25 +6654,25 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.7182</v>
+        <v>0.6596</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2436</v>
+        <v>-0.089</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0037</v>
+        <v>0.1991</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1443</v>
+        <v>0.0718</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5735</v>
+        <v>0.6507</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4265</v>
+        <v>0.3493</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3154</v>
+        <v>1.2461</v>
       </c>
     </row>
     <row r="10">
@@ -6680,25 +6680,25 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1729</v>
+        <v>0.9049</v>
       </c>
       <c r="C10" t="n">
-        <v>0.227</v>
+        <v>-0.1415</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3627</v>
+        <v>-0.1511</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1737</v>
+        <v>-0.049</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6117</v>
+        <v>0.5702</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3883</v>
+        <v>0.4298</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7166</v>
+        <v>1.112</v>
       </c>
     </row>
     <row r="11">
@@ -6706,25 +6706,25 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6596</v>
+        <v>-0.054</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.089</v>
+        <v>0.2262</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1991</v>
+        <v>0.0309</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0718</v>
+        <v>0.5738</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6507</v>
+        <v>0.5348</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3493</v>
+        <v>0.4652</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2461</v>
+        <v>1.3301</v>
       </c>
     </row>
     <row r="12">
@@ -6732,25 +6732,25 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.9049</v>
+        <v>0.0616</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1415</v>
+        <v>0.0385</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1511</v>
+        <v>0.0968</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.049</v>
+        <v>0.6284</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5702</v>
+        <v>0.577</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4298</v>
+        <v>0.423</v>
       </c>
       <c r="H12" t="n">
-        <v>1.112</v>
+        <v>1.0748</v>
       </c>
     </row>
     <row r="13">
@@ -6758,25 +6758,25 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.054</v>
+        <v>0.4857</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2262</v>
+        <v>0.2251</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0309</v>
+        <v>0.1798</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5738</v>
+        <v>0.0261</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5348</v>
+        <v>0.5959</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4652</v>
+        <v>0.4041</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3301</v>
+        <v>1.7233</v>
       </c>
     </row>
     <row r="14">
@@ -6784,25 +6784,25 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0616</v>
+        <v>0.1729</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0385</v>
+        <v>0.227</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0968</v>
+        <v>0.3627</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6284</v>
+        <v>0.1737</v>
       </c>
       <c r="F14" t="n">
-        <v>0.577</v>
+        <v>0.6117</v>
       </c>
       <c r="G14" t="n">
-        <v>0.423</v>
+        <v>0.3883</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0748</v>
+        <v>2.7166</v>
       </c>
     </row>
   </sheetData>
@@ -6838,13 +6838,13 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.659</v>
+        <v>0.8574</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4342</v>
+        <v>0.7352</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5658</v>
+        <v>0.2648</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -6855,13 +6855,13 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6391</v>
+        <v>0.6528</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4085</v>
+        <v>0.4261</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5915</v>
+        <v>0.5739</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -6872,13 +6872,13 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8574</v>
+        <v>0.6162</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7352</v>
+        <v>0.3797</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2648</v>
+        <v>0.6203</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -6889,13 +6889,13 @@
         <v>44</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7699</v>
+        <v>0.7972</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5928</v>
+        <v>0.6355</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4072</v>
+        <v>0.3645</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -6906,13 +6906,13 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.6769</v>
+        <v>0.659</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4582</v>
+        <v>0.4342</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5418</v>
+        <v>0.5658</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -6923,13 +6923,13 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.6528</v>
+        <v>0.6391</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4261</v>
+        <v>0.4085</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5739</v>
+        <v>0.5915</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -6940,13 +6940,13 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.6162</v>
+        <v>0.6769</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3797</v>
+        <v>0.4582</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6203</v>
+        <v>0.5418</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -6957,13 +6957,13 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.7972</v>
+        <v>0.7269</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6355</v>
+        <v>0.5283</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3645</v>
+        <v>0.4717</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -6974,13 +6974,13 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5331</v>
+        <v>0.6171</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2842</v>
+        <v>0.3808</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7158</v>
+        <v>0.6192</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -6991,13 +6991,13 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7269</v>
+        <v>0.6935</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5283</v>
+        <v>0.481</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4717</v>
+        <v>0.519</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -7008,13 +7008,13 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.6171</v>
+        <v>0.5881</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3808</v>
+        <v>0.3459</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6192</v>
+        <v>0.6541</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -7025,13 +7025,13 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.6935</v>
+        <v>0.7699</v>
       </c>
       <c r="C13" t="n">
-        <v>0.481</v>
+        <v>0.5928</v>
       </c>
       <c r="D13" t="n">
-        <v>0.519</v>
+        <v>0.4072</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -7042,13 +7042,13 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.5881</v>
+        <v>0.5331</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3459</v>
+        <v>0.2842</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6541</v>
+        <v>0.7158</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -7090,19 +7090,19 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0944</v>
+        <v>0.731</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6868</v>
+        <v>0.1889</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5654</v>
+        <v>0.7505</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4346</v>
+        <v>0.2495</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0378</v>
+        <v>1.1329</v>
       </c>
     </row>
     <row r="3">
@@ -7110,19 +7110,19 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.261</v>
+        <v>0.7513</v>
       </c>
       <c r="C3" t="n">
-        <v>1.102</v>
+        <v>-0.0755</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9065</v>
+        <v>0.496</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0935</v>
+        <v>0.504</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1118</v>
+        <v>1.0202</v>
       </c>
     </row>
     <row r="4">
@@ -7130,19 +7130,19 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.731</v>
+        <v>0.7244</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1889</v>
+        <v>-0.0849</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7505</v>
+        <v>0.4515</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2495</v>
+        <v>0.5485</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1329</v>
+        <v>1.0275</v>
       </c>
     </row>
     <row r="5">
@@ -7150,19 +7150,19 @@
         <v>44</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8817</v>
+        <v>0.815</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0869</v>
+        <v>0.0132</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6847</v>
+        <v>0.6785</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3153</v>
+        <v>0.3215</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0194</v>
+        <v>1.0005</v>
       </c>
     </row>
     <row r="6">
@@ -7170,19 +7170,19 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.0848</v>
+        <v>0.0944</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9302</v>
+        <v>0.6868</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7694</v>
+        <v>0.5654</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2306</v>
+        <v>0.4346</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0166</v>
+        <v>1.0378</v>
       </c>
     </row>
     <row r="7">
@@ -7190,19 +7190,19 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7513</v>
+        <v>-0.261</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0755</v>
+        <v>1.102</v>
       </c>
       <c r="D7" t="n">
-        <v>0.496</v>
+        <v>0.9065</v>
       </c>
       <c r="E7" t="n">
-        <v>0.504</v>
+        <v>0.0935</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0202</v>
+        <v>1.1118</v>
       </c>
     </row>
     <row r="8">
@@ -7210,19 +7210,19 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7244</v>
+        <v>-0.0848</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0849</v>
+        <v>0.9302</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4515</v>
+        <v>0.7694</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5485</v>
+        <v>0.2306</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0275</v>
+        <v>1.0166</v>
       </c>
     </row>
     <row r="9">
@@ -7230,19 +7230,19 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.815</v>
+        <v>0.8944</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0132</v>
+        <v>-0.1426</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6785</v>
+        <v>0.6536</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3215</v>
+        <v>0.3464</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0005</v>
+        <v>1.0508</v>
       </c>
     </row>
     <row r="10">
@@ -7250,19 +7250,19 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.478</v>
+        <v>0.2569</v>
       </c>
       <c r="C10" t="n">
-        <v>0.084</v>
+        <v>0.4427</v>
       </c>
       <c r="D10" t="n">
-        <v>0.288</v>
+        <v>0.4106</v>
       </c>
       <c r="E10" t="n">
-        <v>0.712</v>
+        <v>0.5894</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0617</v>
+        <v>1.605</v>
       </c>
     </row>
     <row r="11">
@@ -7270,19 +7270,19 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.8944</v>
+        <v>0.4467</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.1426</v>
+        <v>0.3115</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6536</v>
+        <v>0.4785</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3464</v>
+        <v>0.5215</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0508</v>
+        <v>1.7867</v>
       </c>
     </row>
     <row r="12">
@@ -7290,19 +7290,19 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2569</v>
+        <v>0.4175</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4427</v>
+        <v>0.2193</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4106</v>
+        <v>0.3421</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5894</v>
+        <v>0.6579</v>
       </c>
       <c r="F12" t="n">
-        <v>1.605</v>
+        <v>1.5126</v>
       </c>
     </row>
     <row r="13">
@@ -7310,19 +7310,19 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4467</v>
+        <v>0.8817</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3115</v>
+        <v>-0.0869</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4785</v>
+        <v>0.6847</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5215</v>
+        <v>0.3153</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7867</v>
+        <v>1.0194</v>
       </c>
     </row>
     <row r="14">
@@ -7330,19 +7330,19 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.4175</v>
+        <v>0.478</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2193</v>
+        <v>0.084</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3421</v>
+        <v>0.288</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6579</v>
+        <v>0.712</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5126</v>
+        <v>1.0617</v>
       </c>
     </row>
   </sheetData>
@@ -7384,22 +7384,22 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0376</v>
+        <v>0.8889</v>
       </c>
       <c r="C2" t="n">
-        <v>0.264</v>
+        <v>-0.1187</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5474</v>
+        <v>0.2355</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5511</v>
+        <v>0.8991</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4489</v>
+        <v>0.1009</v>
       </c>
       <c r="G2" t="n">
-        <v>1.4524</v>
+        <v>1.1776</v>
       </c>
     </row>
     <row r="3">
@@ -7407,22 +7407,22 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.0645</v>
+        <v>0.7214</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0224</v>
+        <v>0.0442</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9723</v>
+        <v>-0.0334</v>
       </c>
       <c r="E3" t="n">
-        <v>0.911</v>
+        <v>0.5386</v>
       </c>
       <c r="F3" t="n">
-        <v>0.089</v>
+        <v>0.4614</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0099</v>
+        <v>1.0118</v>
       </c>
     </row>
     <row r="4">
@@ -7430,22 +7430,22 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8889</v>
+        <v>0.8003</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1187</v>
+        <v>-0.0896</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2355</v>
+        <v>-0.0163</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8991</v>
+        <v>0.5488</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1009</v>
+        <v>0.4512</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1776</v>
+        <v>1.0259</v>
       </c>
     </row>
     <row r="5">
@@ -7453,22 +7453,22 @@
         <v>44</v>
       </c>
       <c r="B5" t="n">
-        <v>0.3291</v>
+        <v>0.7852</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7752</v>
+        <v>0.0676</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2241</v>
+        <v>0.0479</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8278</v>
+        <v>0.7284</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1722</v>
+        <v>0.2716</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5365</v>
+        <v>1.0223</v>
       </c>
     </row>
     <row r="6">
@@ -7476,22 +7476,22 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2097</v>
+        <v>0.0376</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.1696</v>
+        <v>0.264</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9087</v>
+        <v>0.5474</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8773</v>
+        <v>0.5511</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1227</v>
+        <v>0.4489</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1792</v>
+        <v>1.4524</v>
       </c>
     </row>
     <row r="7">
@@ -7499,22 +7499,22 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7214</v>
+        <v>-0.0645</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0442</v>
+        <v>0.0224</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0334</v>
+        <v>0.9723</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5386</v>
+        <v>0.911</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4614</v>
+        <v>0.089</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0118</v>
+        <v>1.0099</v>
       </c>
     </row>
     <row r="8">
@@ -7522,22 +7522,22 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.8003</v>
+        <v>0.2097</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0896</v>
+        <v>-0.1696</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0163</v>
+        <v>0.9087</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5488</v>
+        <v>0.8773</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4512</v>
+        <v>0.1227</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0259</v>
+        <v>1.1792</v>
       </c>
     </row>
     <row r="9">
@@ -7545,22 +7545,22 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.7852</v>
+        <v>0.43</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0676</v>
+        <v>0.6046</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0479</v>
+        <v>-0.2135</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7284</v>
+        <v>0.699</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2716</v>
+        <v>0.301</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0223</v>
+        <v>2.0911</v>
       </c>
     </row>
     <row r="10">
@@ -7568,22 +7568,22 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.001</v>
+        <v>-0.3145</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6608</v>
+        <v>0.845</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0393</v>
+        <v>0.2611</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4107</v>
+        <v>0.6995</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5893</v>
+        <v>0.3005</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0071</v>
+        <v>1.4809</v>
       </c>
     </row>
     <row r="11">
@@ -7591,22 +7591,22 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.43</v>
+        <v>0.0503</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6046</v>
+        <v>0.6089</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2135</v>
+        <v>0.1781</v>
       </c>
       <c r="E11" t="n">
-        <v>0.699</v>
+        <v>0.5628</v>
       </c>
       <c r="F11" t="n">
-        <v>0.301</v>
+        <v>0.4372</v>
       </c>
       <c r="G11" t="n">
-        <v>2.0911</v>
+        <v>1.1845</v>
       </c>
     </row>
     <row r="12">
@@ -7614,22 +7614,22 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.3145</v>
+        <v>0.3788</v>
       </c>
       <c r="C12" t="n">
-        <v>0.845</v>
+        <v>0.1128</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2611</v>
+        <v>0.2002</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6995</v>
+        <v>0.3447</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3005</v>
+        <v>0.6553</v>
       </c>
       <c r="G12" t="n">
-        <v>1.4809</v>
+        <v>1.7235</v>
       </c>
     </row>
     <row r="13">
@@ -7637,22 +7637,22 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0503</v>
+        <v>0.3291</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6089</v>
+        <v>0.7752</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1781</v>
+        <v>-0.2241</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5628</v>
+        <v>0.8278</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4372</v>
+        <v>0.1722</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1845</v>
+        <v>1.5365</v>
       </c>
     </row>
     <row r="14">
@@ -7660,22 +7660,22 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3788</v>
+        <v>-0.001</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1128</v>
+        <v>0.6608</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2002</v>
+        <v>-0.0393</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3447</v>
+        <v>0.4107</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6553</v>
+        <v>0.5893</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7235</v>
+        <v>1.0071</v>
       </c>
     </row>
   </sheetData>
@@ -7720,25 +7720,25 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1094</v>
+        <v>0.8002</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2283</v>
+        <v>-0.0836</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7245</v>
+        <v>0.2503</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2419</v>
+        <v>0.0634</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7477</v>
+        <v>0.8436</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2523</v>
+        <v>0.1564</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4878</v>
+        <v>1.2314</v>
       </c>
     </row>
     <row r="3">
@@ -7746,25 +7746,25 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.0422</v>
+        <v>0.7163</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0226</v>
+        <v>0.0341</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8853</v>
+        <v>-0.0428</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0668</v>
+        <v>0.0861</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8101</v>
+        <v>0.5718</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1899</v>
+        <v>0.4282</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0173</v>
+        <v>1.0408</v>
       </c>
     </row>
     <row r="4">
@@ -7772,25 +7772,25 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8002</v>
+        <v>0.8244</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.0836</v>
+        <v>-0.1137</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2503</v>
+        <v>0.0347</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0634</v>
+        <v>-0.066</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8436</v>
+        <v>0.569</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1564</v>
+        <v>0.431</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2314</v>
+        <v>1.0547</v>
       </c>
     </row>
     <row r="5">
@@ -7798,25 +7798,25 @@
         <v>44</v>
       </c>
       <c r="B5" t="n">
-        <v>0.3512</v>
+        <v>0.7652</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6944</v>
+        <v>0.035</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1645</v>
+        <v>0.0095</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0235</v>
+        <v>0.2061</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7715</v>
+        <v>0.7992</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2285</v>
+        <v>0.2008</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6135</v>
+        <v>1.1492</v>
       </c>
     </row>
     <row r="6">
@@ -7824,25 +7824,25 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1024</v>
+        <v>0.1094</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.1348</v>
+        <v>0.2283</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8063</v>
+        <v>0.7245</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2645</v>
+        <v>-0.2419</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8362</v>
+        <v>0.7477</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1638</v>
+        <v>0.2523</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3098</v>
+        <v>1.4878</v>
       </c>
     </row>
     <row r="7">
@@ -7850,25 +7850,25 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7163</v>
+        <v>-0.0422</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0341</v>
+        <v>0.0226</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0428</v>
+        <v>0.8853</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0861</v>
+        <v>0.0668</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5718</v>
+        <v>0.8101</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4282</v>
+        <v>0.1899</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0408</v>
+        <v>1.0173</v>
       </c>
     </row>
     <row r="8">
@@ -7876,25 +7876,25 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.8244</v>
+        <v>0.1024</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.1137</v>
+        <v>-0.1348</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0347</v>
+        <v>0.8063</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.066</v>
+        <v>0.2645</v>
       </c>
       <c r="F8" t="n">
-        <v>0.569</v>
+        <v>0.8362</v>
       </c>
       <c r="G8" t="n">
-        <v>0.431</v>
+        <v>0.1638</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0547</v>
+        <v>1.3098</v>
       </c>
     </row>
     <row r="9">
@@ -7902,25 +7902,25 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.7652</v>
+        <v>0.5362</v>
       </c>
       <c r="C9" t="n">
-        <v>0.035</v>
+        <v>0.5331</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0095</v>
+        <v>-0.1234</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2061</v>
+        <v>-0.1776</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7992</v>
+        <v>0.717</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2008</v>
+        <v>0.283</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1492</v>
+        <v>2.3229</v>
       </c>
     </row>
     <row r="10">
@@ -7928,25 +7928,25 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.1125</v>
+        <v>-0.207</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7064</v>
+        <v>0.7692</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0951</v>
+        <v>0.2968</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2505</v>
+        <v>-0.082</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4958</v>
+        <v>0.6695</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5042</v>
+        <v>0.3305</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3445</v>
+        <v>1.4786</v>
       </c>
     </row>
     <row r="11">
@@ -7954,25 +7954,25 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5362</v>
+        <v>0.016</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5331</v>
+        <v>0.5978</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1234</v>
+        <v>0.1701</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1776</v>
+        <v>0.1275</v>
       </c>
       <c r="F11" t="n">
-        <v>0.717</v>
+        <v>0.572</v>
       </c>
       <c r="G11" t="n">
-        <v>0.283</v>
+        <v>0.428</v>
       </c>
       <c r="H11" t="n">
-        <v>2.3229</v>
+        <v>1.2596</v>
       </c>
     </row>
     <row r="12">
@@ -7980,25 +7980,25 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.207</v>
+        <v>0.1112</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7692</v>
+        <v>0.1691</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2968</v>
+        <v>0.0593</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.082</v>
+        <v>0.6228</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6695</v>
+        <v>0.6069</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3305</v>
+        <v>0.3931</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4786</v>
+        <v>1.2345</v>
       </c>
     </row>
     <row r="13">
@@ -8006,25 +8006,25 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.016</v>
+        <v>0.3512</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5978</v>
+        <v>0.6944</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1701</v>
+        <v>-0.1645</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1275</v>
+        <v>0.0235</v>
       </c>
       <c r="F13" t="n">
-        <v>0.572</v>
+        <v>0.7715</v>
       </c>
       <c r="G13" t="n">
-        <v>0.428</v>
+        <v>0.2285</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2596</v>
+        <v>1.6135</v>
       </c>
     </row>
     <row r="14">
@@ -8032,25 +8032,25 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1112</v>
+        <v>-0.1125</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1691</v>
+        <v>0.7064</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0593</v>
+        <v>-0.0951</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6228</v>
+        <v>0.2505</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6069</v>
+        <v>0.4958</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3931</v>
+        <v>0.5042</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2345</v>
+        <v>1.3445</v>
       </c>
     </row>
   </sheetData>
@@ -8086,13 +8086,13 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6541</v>
+        <v>0.6579</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4279</v>
+        <v>0.4328</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5721</v>
+        <v>0.5672</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -8103,13 +8103,13 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6665</v>
+        <v>0.549</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4442</v>
+        <v>0.3014</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5558</v>
+        <v>0.6986</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -8120,13 +8120,13 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6579</v>
+        <v>0.6292</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4328</v>
+        <v>0.3959</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5672</v>
+        <v>0.6041</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -8137,13 +8137,13 @@
         <v>44</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6586</v>
+        <v>0.7172</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4338</v>
+        <v>0.5144</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5662</v>
+        <v>0.4856</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -8154,13 +8154,13 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7188</v>
+        <v>0.6541</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5167</v>
+        <v>0.4279</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4833</v>
+        <v>0.5721</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -8171,13 +8171,13 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.549</v>
+        <v>0.6665</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3014</v>
+        <v>0.4442</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6986</v>
+        <v>0.5558</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -8188,13 +8188,13 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.6292</v>
+        <v>0.7188</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3959</v>
+        <v>0.5167</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6041</v>
+        <v>0.4833</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -8205,13 +8205,13 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.7172</v>
+        <v>0.6219</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5144</v>
+        <v>0.3867</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4856</v>
+        <v>0.6133</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -8222,13 +8222,13 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5917</v>
+        <v>0.5658</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3501</v>
+        <v>0.3202</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6499</v>
+        <v>0.6798</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -8239,13 +8239,13 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6219</v>
+        <v>0.641</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3867</v>
+        <v>0.4108</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6133</v>
+        <v>0.5892</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -8256,13 +8256,13 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.5658</v>
+        <v>0.6903</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3202</v>
+        <v>0.4766</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6798</v>
+        <v>0.5234</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -8273,13 +8273,13 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.641</v>
+        <v>0.6586</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4108</v>
+        <v>0.4338</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5892</v>
+        <v>0.5662</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -8290,13 +8290,13 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6903</v>
+        <v>0.5917</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4766</v>
+        <v>0.3501</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5234</v>
+        <v>0.6499</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -8338,19 +8338,19 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.0493</v>
+        <v>0.3443</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8094</v>
+        <v>0.3716</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6039</v>
+        <v>0.4288</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3961</v>
+        <v>0.5712</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0074</v>
+        <v>1.9884</v>
       </c>
     </row>
     <row r="3">
@@ -8358,19 +8358,19 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.188</v>
+        <v>0.4757</v>
       </c>
       <c r="C3" t="n">
-        <v>0.991</v>
+        <v>0.1044</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7669</v>
+        <v>0.3039</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2331</v>
+        <v>0.6961</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0719</v>
+        <v>1.0961</v>
       </c>
     </row>
     <row r="4">
@@ -8378,19 +8378,19 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3443</v>
+        <v>0.8377</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3716</v>
+        <v>-0.1644</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4288</v>
+        <v>0.5435</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5712</v>
+        <v>0.4565</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9884</v>
+        <v>1.0769</v>
       </c>
     </row>
     <row r="5">
@@ -8398,19 +8398,19 @@
         <v>44</v>
       </c>
       <c r="B5" t="n">
-        <v>0.733</v>
+        <v>0.6087</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0319</v>
+        <v>0.1618</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5069</v>
+        <v>0.5292</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4931</v>
+        <v>0.4708</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0038</v>
+        <v>1.1406</v>
       </c>
     </row>
     <row r="6">
@@ -8418,19 +8418,19 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.0843</v>
+        <v>-0.0493</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9362</v>
+        <v>0.8094</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7774</v>
+        <v>0.6039</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2226</v>
+        <v>0.3961</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0162</v>
+        <v>1.0074</v>
       </c>
     </row>
     <row r="7">
@@ -8438,19 +8438,19 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4757</v>
+        <v>-0.188</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1044</v>
+        <v>0.991</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3039</v>
+        <v>0.7669</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6961</v>
+        <v>0.2331</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0961</v>
+        <v>1.0719</v>
       </c>
     </row>
     <row r="8">
@@ -8458,19 +8458,19 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.8377</v>
+        <v>-0.0843</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.1644</v>
+        <v>0.9362</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5435</v>
+        <v>0.7774</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4565</v>
+        <v>0.2226</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0769</v>
+        <v>1.0162</v>
       </c>
     </row>
     <row r="9">
@@ -8478,19 +8478,19 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.6087</v>
+        <v>0.8244</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1618</v>
+        <v>-0.1594</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5292</v>
+        <v>0.5283</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4708</v>
+        <v>0.4717</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1406</v>
+        <v>1.0747</v>
       </c>
     </row>
     <row r="10">
@@ -8498,19 +8498,19 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4147</v>
+        <v>0.6888</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2141</v>
+        <v>-0.0855</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3372</v>
+        <v>0.4025</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6628</v>
+        <v>0.5975</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4977</v>
+        <v>1.0308</v>
       </c>
     </row>
     <row r="11">
@@ -8518,19 +8518,19 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.8244</v>
+        <v>0.4064</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.1594</v>
+        <v>0.2845</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5283</v>
+        <v>0.4016</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4717</v>
+        <v>0.5984</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0747</v>
+        <v>1.7902</v>
       </c>
     </row>
     <row r="12">
@@ -8538,19 +8538,19 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.6888</v>
+        <v>0.4263</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.0855</v>
+        <v>0.3178</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4025</v>
+        <v>0.4649</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5975</v>
+        <v>0.5351</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0308</v>
+        <v>1.849</v>
       </c>
     </row>
     <row r="13">
@@ -8558,19 +8558,19 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4064</v>
+        <v>0.733</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2845</v>
+        <v>-0.0319</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4016</v>
+        <v>0.5069</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5984</v>
+        <v>0.4931</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7902</v>
+        <v>1.0038</v>
       </c>
     </row>
     <row r="14">
@@ -8578,19 +8578,19 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.4263</v>
+        <v>0.4147</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3178</v>
+        <v>0.2141</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4649</v>
+        <v>0.3372</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5351</v>
+        <v>0.6628</v>
       </c>
       <c r="F14" t="n">
-        <v>1.849</v>
+        <v>1.4977</v>
       </c>
     </row>
   </sheetData>
@@ -8632,22 +8632,22 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.0355</v>
+        <v>-0.3424</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7233</v>
+        <v>0.1843</v>
       </c>
       <c r="D2" t="n">
-        <v>0.107</v>
+        <v>1.056</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5848</v>
+        <v>0.9377</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4152</v>
+        <v>0.0623</v>
       </c>
       <c r="G2" t="n">
-        <v>1.0487</v>
+        <v>1.2743</v>
       </c>
     </row>
     <row r="3">
@@ -8655,22 +8655,22 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.0816</v>
+        <v>0.0769</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9479</v>
+        <v>-0.0201</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0281</v>
+        <v>0.609</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7886</v>
+        <v>0.4224</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2114</v>
+        <v>0.5776</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0166</v>
+        <v>1.0341</v>
       </c>
     </row>
     <row r="4">
@@ -8678,22 +8678,22 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.3424</v>
+        <v>0.5092</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1843</v>
+        <v>-0.2293</v>
       </c>
       <c r="D4" t="n">
-        <v>1.056</v>
+        <v>0.4642</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9377</v>
+        <v>0.5783</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0623</v>
+        <v>0.4217</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2743</v>
+        <v>2.3885</v>
       </c>
     </row>
     <row r="5">
@@ -8701,22 +8701,22 @@
         <v>44</v>
       </c>
       <c r="B5" t="n">
-        <v>0.587</v>
+        <v>0.4341</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.035</v>
+        <v>0.1261</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1951</v>
+        <v>0.2618</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4998</v>
+        <v>0.5199</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5002</v>
+        <v>0.4801</v>
       </c>
       <c r="G5" t="n">
-        <v>1.226</v>
+        <v>1.8401</v>
       </c>
     </row>
     <row r="6">
@@ -8724,22 +8724,22 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.0212</v>
+        <v>-0.0355</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8796</v>
+        <v>0.7233</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0345</v>
+        <v>0.107</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7854</v>
+        <v>0.5848</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2146</v>
+        <v>0.4152</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0042</v>
+        <v>1.0487</v>
       </c>
     </row>
     <row r="7">
@@ -8747,22 +8747,22 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0769</v>
+        <v>-0.0816</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0201</v>
+        <v>0.9479</v>
       </c>
       <c r="D7" t="n">
-        <v>0.609</v>
+        <v>-0.0281</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4224</v>
+        <v>0.7886</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5776</v>
+        <v>0.2114</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0341</v>
+        <v>1.0166</v>
       </c>
     </row>
     <row r="8">
@@ -8770,22 +8770,22 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.5092</v>
+        <v>-0.0212</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2293</v>
+        <v>0.8796</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4642</v>
+        <v>0.0345</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5783</v>
+        <v>0.7854</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4217</v>
+        <v>0.2146</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3885</v>
+        <v>1.0042</v>
       </c>
     </row>
     <row r="9">
@@ -8793,22 +8793,22 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4341</v>
+        <v>0.7921</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1261</v>
+        <v>-0.1242</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2618</v>
+        <v>0.0331</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5199</v>
+        <v>0.557</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4801</v>
+        <v>0.443</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8401</v>
+        <v>1.0528</v>
       </c>
     </row>
     <row r="10">
@@ -8816,22 +8816,22 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2898</v>
+        <v>0.9279</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1799</v>
+        <v>-0.0196</v>
       </c>
       <c r="D10" t="n">
-        <v>0.202</v>
+        <v>-0.2826</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3336</v>
+        <v>0.5878</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6664</v>
+        <v>0.4122</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5288</v>
+        <v>1.1849</v>
       </c>
     </row>
     <row r="11">
@@ -8839,22 +8839,22 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7921</v>
+        <v>0.5259</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.1242</v>
+        <v>0.3251</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0331</v>
+        <v>-0.1354</v>
       </c>
       <c r="E11" t="n">
-        <v>0.557</v>
+        <v>0.4629</v>
       </c>
       <c r="F11" t="n">
-        <v>0.443</v>
+        <v>0.5371</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0528</v>
+        <v>1.8235</v>
       </c>
     </row>
     <row r="12">
@@ -8862,22 +8862,22 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.9279</v>
+        <v>0.4329</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.0196</v>
+        <v>0.3225</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2826</v>
+        <v>0.0214</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5878</v>
+        <v>0.4763</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4122</v>
+        <v>0.5237</v>
       </c>
       <c r="G12" t="n">
-        <v>1.1849</v>
+        <v>1.8544</v>
       </c>
     </row>
     <row r="13">
@@ -8885,22 +8885,22 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5259</v>
+        <v>0.587</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3251</v>
+        <v>-0.035</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1354</v>
+        <v>0.1951</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4629</v>
+        <v>0.4998</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5371</v>
+        <v>0.5002</v>
       </c>
       <c r="G13" t="n">
-        <v>1.8235</v>
+        <v>1.226</v>
       </c>
     </row>
     <row r="14">
@@ -8908,22 +8908,22 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.4329</v>
+        <v>0.2898</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3225</v>
+        <v>0.1799</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0214</v>
+        <v>0.202</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4763</v>
+        <v>0.3336</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5237</v>
+        <v>0.6664</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8544</v>
+        <v>2.5288</v>
       </c>
     </row>
   </sheetData>
@@ -8968,25 +8968,25 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6698</v>
+        <v>0.2463</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0133</v>
+        <v>0.0953</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0949</v>
+        <v>-0.1126</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0817</v>
+        <v>0.7611</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5796</v>
+        <v>0.7991</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4204</v>
+        <v>0.2009</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0713</v>
+        <v>1.2897</v>
       </c>
     </row>
     <row r="3">
@@ -8994,25 +8994,25 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8324</v>
+        <v>-0.1287</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.1257</v>
+        <v>-0.0251</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1544</v>
+        <v>0.2974</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0012</v>
+        <v>0.6412</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7592</v>
+        <v>0.5346</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2408</v>
+        <v>0.4654</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1158</v>
+        <v>1.5077</v>
       </c>
     </row>
     <row r="4">
@@ -9020,25 +9020,25 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2463</v>
+        <v>-0.0622</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0953</v>
+        <v>0.8606</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1126</v>
+        <v>-0.2135</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7611</v>
+        <v>0.3051</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7991</v>
+        <v>0.7863</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2009</v>
+        <v>0.2137</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2897</v>
+        <v>1.3946</v>
       </c>
     </row>
     <row r="5">
@@ -9046,25 +9046,25 @@
         <v>44</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.1114</v>
+        <v>0.2156</v>
       </c>
       <c r="C5" t="n">
-        <v>0.275</v>
+        <v>0.5128</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4816</v>
+        <v>0.0345</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1808</v>
+        <v>0.1499</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5238</v>
+        <v>0.5592</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4762</v>
+        <v>0.4408</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0476</v>
+        <v>1.5451</v>
       </c>
     </row>
     <row r="6">
@@ -9072,25 +9072,25 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9226</v>
+        <v>0.6698</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0838</v>
+        <v>-0.0133</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0357</v>
+        <v>0.0949</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0284</v>
+        <v>0.0817</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8629</v>
+        <v>0.5796</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1371</v>
+        <v>0.4204</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0215</v>
+        <v>1.0713</v>
       </c>
     </row>
     <row r="7">
@@ -9098,25 +9098,25 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.1287</v>
+        <v>0.8324</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0251</v>
+        <v>-0.1257</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2974</v>
+        <v>0.1544</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6412</v>
+        <v>-0.0012</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5346</v>
+        <v>0.7592</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4654</v>
+        <v>0.2408</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5077</v>
+        <v>1.1158</v>
       </c>
     </row>
     <row r="8">
@@ -9124,25 +9124,25 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.0622</v>
+        <v>0.9226</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8606</v>
+        <v>0.0838</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2135</v>
+        <v>-0.0357</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3051</v>
+        <v>-0.0284</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7863</v>
+        <v>0.8629</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2137</v>
+        <v>0.1371</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3946</v>
+        <v>1.0215</v>
       </c>
     </row>
     <row r="9">
@@ -9150,25 +9150,25 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2156</v>
+        <v>-0.0969</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5128</v>
+        <v>0.5288</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0345</v>
+        <v>0.3437</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1499</v>
+        <v>-0.0085</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5592</v>
+        <v>0.5421</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4408</v>
+        <v>0.4579</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5451</v>
+        <v>1.7978</v>
       </c>
     </row>
     <row r="10">
@@ -9176,25 +9176,25 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0069</v>
+        <v>0.0144</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0882</v>
+        <v>0.6091</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5586</v>
+        <v>0.3604</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2689</v>
+        <v>-0.3224</v>
       </c>
       <c r="F10" t="n">
-        <v>0.438</v>
+        <v>0.6175</v>
       </c>
       <c r="G10" t="n">
-        <v>0.562</v>
+        <v>0.3825</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4982</v>
+        <v>2.2142</v>
       </c>
     </row>
     <row r="11">
@@ -9202,25 +9202,25 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.0969</v>
+        <v>0.1864</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5288</v>
+        <v>0.0783</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3437</v>
+        <v>0.5792</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0085</v>
+        <v>-0.0917</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5421</v>
+        <v>0.5082</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4579</v>
+        <v>0.4918</v>
       </c>
       <c r="H11" t="n">
-        <v>1.7978</v>
+        <v>1.3001</v>
       </c>
     </row>
     <row r="12">
@@ -9228,25 +9228,25 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0144</v>
+        <v>0.1693</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6091</v>
+        <v>0.0115</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3604</v>
+        <v>0.5836</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3224</v>
+        <v>0.0676</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6175</v>
+        <v>0.536</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3825</v>
+        <v>0.464</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2142</v>
+        <v>1.1968</v>
       </c>
     </row>
     <row r="13">
@@ -9254,25 +9254,25 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1864</v>
+        <v>-0.1114</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0783</v>
+        <v>0.275</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5792</v>
+        <v>0.4816</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0917</v>
+        <v>0.1808</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5082</v>
+        <v>0.5238</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4918</v>
+        <v>0.4762</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3001</v>
+        <v>2.0476</v>
       </c>
     </row>
     <row r="14">
@@ -9280,25 +9280,25 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1693</v>
+        <v>0.0069</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0115</v>
+        <v>-0.0882</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5836</v>
+        <v>0.5586</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0676</v>
+        <v>0.2689</v>
       </c>
       <c r="F14" t="n">
-        <v>0.536</v>
+        <v>0.438</v>
       </c>
       <c r="G14" t="n">
-        <v>0.464</v>
+        <v>0.562</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1968</v>
+        <v>1.4982</v>
       </c>
     </row>
   </sheetData>
@@ -9334,13 +9334,13 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7673</v>
+        <v>0.6718</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5887</v>
+        <v>0.4512</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4113</v>
+        <v>0.5488</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -9351,13 +9351,13 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7008</v>
+        <v>0.353</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4912</v>
+        <v>0.1246</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5088</v>
+        <v>0.8754</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -9368,13 +9368,13 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6718</v>
+        <v>0.4873</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4512</v>
+        <v>0.2374</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5488</v>
+        <v>0.7626</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -9385,13 +9385,13 @@
         <v>44</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5403</v>
+        <v>0.6006</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2919</v>
+        <v>0.3608</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7081</v>
+        <v>0.6392</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -9402,13 +9402,13 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8368</v>
+        <v>0.7673</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7003</v>
+        <v>0.5887</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2997</v>
+        <v>0.4113</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -9419,13 +9419,13 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.353</v>
+        <v>0.7008</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1246</v>
+        <v>0.4912</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8754</v>
+        <v>0.5088</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -9436,13 +9436,13 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>0.4873</v>
+        <v>0.8368</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2374</v>
+        <v>0.7003</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7626</v>
+        <v>0.2997</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -9453,13 +9453,13 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.6006</v>
+        <v>0.4892</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3608</v>
+        <v>0.2393</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6392</v>
+        <v>0.7607</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -9470,13 +9470,13 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4571</v>
+        <v>0.3744</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2089</v>
+        <v>0.1402</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7911</v>
+        <v>0.8598</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -9487,13 +9487,13 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.4892</v>
+        <v>0.532</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2393</v>
+        <v>0.283</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7607</v>
+        <v>0.717</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -9504,13 +9504,13 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3744</v>
+        <v>0.6886</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1402</v>
+        <v>0.4742</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8598</v>
+        <v>0.5258</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -9521,13 +9521,13 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.532</v>
+        <v>0.5403</v>
       </c>
       <c r="C13" t="n">
-        <v>0.283</v>
+        <v>0.2919</v>
       </c>
       <c r="D13" t="n">
-        <v>0.717</v>
+        <v>0.7081</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -9538,13 +9538,13 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6886</v>
+        <v>0.4571</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4742</v>
+        <v>0.2089</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5258</v>
+        <v>0.7911</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -9586,19 +9586,19 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9154</v>
+        <v>0.1931</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1068</v>
+        <v>0.6227</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7357</v>
+        <v>0.5647</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2643</v>
+        <v>0.4353</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0272</v>
+        <v>1.1905</v>
       </c>
     </row>
     <row r="3">
@@ -9606,19 +9606,19 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9858</v>
+        <v>-0.3256</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.2668</v>
+        <v>0.8682</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7375</v>
+        <v>0.5315</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2625</v>
+        <v>0.4685</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1458</v>
+        <v>1.2757</v>
       </c>
     </row>
     <row r="4">
@@ -9626,19 +9626,19 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1931</v>
+        <v>-0.092</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6227</v>
+        <v>0.7443</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5647</v>
+        <v>0.4828</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4353</v>
+        <v>0.5172</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1905</v>
+        <v>1.0306</v>
       </c>
     </row>
     <row r="5">
@@ -9646,19 +9646,19 @@
         <v>44</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0503</v>
+        <v>0.5394</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6332</v>
+        <v>0.1015</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4404</v>
+        <v>0.3649</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5596</v>
+        <v>0.6351</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0126</v>
+        <v>1.0707</v>
       </c>
     </row>
     <row r="6">
@@ -9666,19 +9666,19 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>1.0299</v>
+        <v>0.9154</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.1453</v>
+        <v>-0.1068</v>
       </c>
       <c r="D6" t="n">
-        <v>0.908</v>
+        <v>0.7357</v>
       </c>
       <c r="E6" t="n">
-        <v>0.092</v>
+        <v>0.2643</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0398</v>
+        <v>1.0272</v>
       </c>
     </row>
     <row r="7">
@@ -9686,19 +9686,19 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.3256</v>
+        <v>0.9858</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8682</v>
+        <v>-0.2668</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5315</v>
+        <v>0.7375</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4685</v>
+        <v>0.2625</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2757</v>
+        <v>1.1458</v>
       </c>
     </row>
     <row r="8">
@@ -9706,19 +9706,19 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.092</v>
+        <v>1.0299</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7443</v>
+        <v>-0.1453</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4828</v>
+        <v>0.908</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5172</v>
+        <v>0.092</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0306</v>
+        <v>1.0398</v>
       </c>
     </row>
     <row r="9">
@@ -9726,19 +9726,19 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5394</v>
+        <v>0.1283</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1015</v>
+        <v>0.4602</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3649</v>
+        <v>0.2969</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6351</v>
+        <v>0.7031</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0707</v>
+        <v>1.1546</v>
       </c>
     </row>
     <row r="10">
@@ -9746,19 +9746,19 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2508</v>
+        <v>0.2605</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2722</v>
+        <v>0.147</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2163</v>
+        <v>0.1339</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7837</v>
+        <v>0.8661</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9868</v>
+        <v>1.5778</v>
       </c>
     </row>
     <row r="11">
@@ -9766,19 +9766,19 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1283</v>
+        <v>0.5423</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4602</v>
+        <v>0.0043</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2969</v>
+        <v>0.2968</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7031</v>
+        <v>0.7032</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1546</v>
+        <v>1.0001</v>
       </c>
     </row>
     <row r="12">
@@ -9786,19 +9786,19 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2605</v>
+        <v>0.5141</v>
       </c>
       <c r="C12" t="n">
-        <v>0.147</v>
+        <v>0.2315</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1339</v>
+        <v>0.4562</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8661</v>
+        <v>0.5438</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5778</v>
+        <v>1.3896</v>
       </c>
     </row>
     <row r="13">
@@ -9806,19 +9806,19 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5423</v>
+        <v>0.0503</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0043</v>
+        <v>0.6332</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2968</v>
+        <v>0.4404</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7032</v>
+        <v>0.5596</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0001</v>
+        <v>1.0126</v>
       </c>
     </row>
     <row r="14">
@@ -9826,19 +9826,19 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.5141</v>
+        <v>0.2508</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2315</v>
+        <v>0.2722</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4562</v>
+        <v>0.2163</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5438</v>
+        <v>0.7837</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3896</v>
+        <v>1.9868</v>
       </c>
     </row>
   </sheetData>
@@ -9880,22 +9880,22 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9821</v>
+        <v>0.3045</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0987</v>
+        <v>0.6964</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2506</v>
+        <v>-0.0861</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8586</v>
+        <v>0.6886</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1414</v>
+        <v>0.3114</v>
       </c>
       <c r="G2" t="n">
-        <v>1.151</v>
+        <v>1.4038</v>
       </c>
     </row>
     <row r="3">
@@ -9903,22 +9903,22 @@
         <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9246</v>
+        <v>-0.2122</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.1512</v>
+        <v>0.9601</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0451</v>
+        <v>-0.0755</v>
       </c>
       <c r="E3" t="n">
-        <v>0.728</v>
+        <v>0.7602</v>
       </c>
       <c r="F3" t="n">
-        <v>0.272</v>
+        <v>0.2398</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0583</v>
+        <v>1.1104</v>
       </c>
     </row>
     <row r="4">
@@ -9926,22 +9926,22 @@
         <v>43</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3045</v>
+        <v>-0.1459</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6964</v>
+        <v>0.4351</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0861</v>
+        <v>0.5023</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6886</v>
+        <v>0.5134</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3114</v>
+        <v>0.4866</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4038</v>
+        <v>2.1439</v>
       </c>
     </row>
     <row r="5">
@@ -9949,22 +9949,22 @@
         <v>44</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.0216</v>
+        <v>0.5101</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3432</v>
+        <v>0.0876</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4973</v>
+        <v>0.0838</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4854</v>
+        <v>0.3597</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5146</v>
+        <v>0.6403</v>
       </c>
       <c r="G5" t="n">
-        <v>1.781</v>
+        <v>1.1143</v>
       </c>
     </row>
     <row r="6">
@@ -9972,22 +9972,22 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9262</v>
+        <v>0.9821</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.1375</v>
+        <v>0.0987</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1335</v>
+        <v>-0.2506</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8939</v>
+        <v>0.8586</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1061</v>
+        <v>0.1414</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0865</v>
+        <v>1.151</v>
       </c>
     </row>
     <row r="7">
@@ -9995,22 +9995,22 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.2122</v>
+        <v>0.9246</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9601</v>
+        <v>-0.1512</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0755</v>
+        <v>-0.0451</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7602</v>
+        <v>0.728</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2398</v>
+        <v>0.272</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1104</v>
+        <v>1.0583</v>
       </c>
     </row>
     <row r="8">
@@ -10018,22 +10018,22 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.1459</v>
+        <v>0.9262</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4351</v>
+        <v>-0.1375</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5023</v>
+        <v>0.1335</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5134</v>
+        <v>0.8939</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4866</v>
+        <v>0.1061</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1439</v>
+        <v>1.0865</v>
       </c>
     </row>
     <row r="9">
@@ -10041,22 +10041,22 @@
         <v>48</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5101</v>
+        <v>-0.0604</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0876</v>
+        <v>0.0729</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0838</v>
+        <v>0.7468</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3597</v>
+        <v>0.5626</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6403</v>
+        <v>0.4374</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1143</v>
+        <v>1.0322</v>
       </c>
     </row>
     <row r="10">
@@ -10064,22 +10064,22 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2856</v>
+        <v>0.0731</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3136</v>
+        <v>-0.2192</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0297</v>
+        <v>0.6718</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2399</v>
+        <v>0.4213</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7601</v>
+        <v>0.5787</v>
       </c>
       <c r="G10" t="n">
-        <v>2.0021</v>
+        <v>1.2364</v>
       </c>
     </row>
     <row r="11">
@@ -10087,22 +10087,22 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.0604</v>
+        <v>0.4371</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0729</v>
+        <v>-0.1609</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7468</v>
+        <v>0.3277</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5626</v>
+        <v>0.3628</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4374</v>
+        <v>0.6372</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0322</v>
+        <v>2.1599</v>
       </c>
     </row>
     <row r="12">
@@ -10110,22 +10110,22 @@
         <v>51</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0731</v>
+        <v>0.5254</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.2192</v>
+        <v>0.2442</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6718</v>
+        <v>0.0428</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4213</v>
+        <v>0.4748</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5787</v>
+        <v>0.5252</v>
       </c>
       <c r="G12" t="n">
-        <v>1.2364</v>
+        <v>1.4282</v>
       </c>
     </row>
     <row r="13">
@@ -10133,22 +10133,22 @@
         <v>52</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4371</v>
+        <v>-0.0216</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.1609</v>
+        <v>0.3432</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3277</v>
+        <v>0.4973</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3628</v>
+        <v>0.4854</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6372</v>
+        <v>0.5146</v>
       </c>
       <c r="G13" t="n">
-        <v>2.1599</v>
+        <v>1.781</v>
       </c>
     </row>
     <row r="14">
@@ -10156,22 +10156,22 @@
         <v>53</v>
       </c>
       <c r="B14" t="n">
-        <v>0.5254</v>
+        <v>0.2856</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2442</v>
+        <v>0.3136</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0428</v>
+        <v>-0.0297</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4748</v>
+        <v>0.2399</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5252</v>
+        <v>0.7601</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4282</v>
+        <v>2.0021</v>
       </c>
     </row>
   </sheetData>

--- a/Reproduce6 - AnalysisBySystem/Data_Analysis/generatedData/EFA_Summary_Consolidated.xlsx
+++ b/Reproduce6 - AnalysisBySystem/Data_Analysis/generatedData/EFA_Summary_Consolidated.xlsx
@@ -596,25 +596,25 @@
         <v>5.41</v>
       </c>
       <c r="G2" t="n">
-        <v>0.742</v>
+        <v>0.706</v>
       </c>
       <c r="H2" t="n">
         <v>0.888</v>
       </c>
       <c r="I2" t="n">
-        <v>0.366</v>
+        <v>0.359</v>
       </c>
       <c r="J2" t="n">
         <v>0.533</v>
       </c>
       <c r="K2" t="n">
-        <v>0.273</v>
+        <v>0.274</v>
       </c>
       <c r="L2" t="n">
         <v>0.283</v>
       </c>
       <c r="M2" t="n">
-        <v>0.195</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="3">
@@ -628,7 +628,7 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -637,25 +637,25 @@
         <v>4.609</v>
       </c>
       <c r="G3" t="n">
-        <v>1.218</v>
+        <v>1.239</v>
       </c>
       <c r="H3" t="n">
         <v>1.194</v>
       </c>
       <c r="I3" t="n">
-        <v>0.779</v>
+        <v>0.778</v>
       </c>
       <c r="J3" t="n">
         <v>0.721</v>
       </c>
       <c r="K3" t="n">
-        <v>0.576</v>
+        <v>0.577</v>
       </c>
       <c r="L3" t="n">
         <v>0.46</v>
       </c>
       <c r="M3" t="n">
-        <v>0.416</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="4">
@@ -678,25 +678,25 @@
         <v>6.006</v>
       </c>
       <c r="G4" t="n">
-        <v>1.311</v>
+        <v>1.314</v>
       </c>
       <c r="H4" t="n">
         <v>1.267</v>
       </c>
       <c r="I4" t="n">
-        <v>0.847</v>
+        <v>0.863</v>
       </c>
       <c r="J4" t="n">
         <v>0.808</v>
       </c>
       <c r="K4" t="n">
-        <v>0.608</v>
+        <v>0.632</v>
       </c>
       <c r="L4" t="n">
         <v>0.334</v>
       </c>
       <c r="M4" t="n">
-        <v>0.432</v>
+        <v>0.438</v>
       </c>
     </row>
     <row r="5">
@@ -719,19 +719,19 @@
         <v>5.935</v>
       </c>
       <c r="G5" t="n">
-        <v>1.446</v>
+        <v>1.482</v>
       </c>
       <c r="H5" t="n">
         <v>0.785</v>
       </c>
       <c r="I5" t="n">
-        <v>0.934</v>
+        <v>0.923</v>
       </c>
       <c r="J5" t="n">
         <v>0.73</v>
       </c>
       <c r="K5" t="n">
-        <v>0.678</v>
+        <v>0.674</v>
       </c>
       <c r="L5" t="n">
         <v>0.418</v>
@@ -760,25 +760,25 @@
         <v>6.396</v>
       </c>
       <c r="G6" t="n">
-        <v>1.239</v>
+        <v>1.275</v>
       </c>
       <c r="H6" t="n">
         <v>1.442</v>
       </c>
       <c r="I6" t="n">
-        <v>0.804</v>
+        <v>0.818</v>
       </c>
       <c r="J6" t="n">
         <v>0.363</v>
       </c>
       <c r="K6" t="n">
-        <v>0.595</v>
+        <v>0.603</v>
       </c>
       <c r="L6" t="n">
         <v>0.346</v>
       </c>
       <c r="M6" t="n">
-        <v>0.418</v>
+        <v>0.422</v>
       </c>
     </row>
     <row r="7">
@@ -801,25 +801,25 @@
         <v>6.087</v>
       </c>
       <c r="G7" t="n">
-        <v>1.286</v>
+        <v>1.284</v>
       </c>
       <c r="H7" t="n">
         <v>1.02</v>
       </c>
       <c r="I7" t="n">
-        <v>0.815</v>
+        <v>0.825</v>
       </c>
       <c r="J7" t="n">
         <v>0.806</v>
       </c>
       <c r="K7" t="n">
-        <v>0.607</v>
+        <v>0.6</v>
       </c>
       <c r="L7" t="n">
         <v>0.308</v>
       </c>
       <c r="M7" t="n">
-        <v>0.425</v>
+        <v>0.418</v>
       </c>
     </row>
   </sheetData>

--- a/Reproduce6 - AnalysisBySystem/Data_Analysis/generatedData/EFA_Summary_Consolidated.xlsx
+++ b/Reproduce6 - AnalysisBySystem/Data_Analysis/generatedData/EFA_Summary_Consolidated.xlsx
@@ -596,19 +596,19 @@
         <v>5.41</v>
       </c>
       <c r="G2" t="n">
-        <v>0.706</v>
+        <v>0.755</v>
       </c>
       <c r="H2" t="n">
         <v>0.888</v>
       </c>
       <c r="I2" t="n">
-        <v>0.359</v>
+        <v>0.363</v>
       </c>
       <c r="J2" t="n">
         <v>0.533</v>
       </c>
       <c r="K2" t="n">
-        <v>0.274</v>
+        <v>0.275</v>
       </c>
       <c r="L2" t="n">
         <v>0.283</v>
@@ -628,7 +628,7 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -637,25 +637,25 @@
         <v>4.609</v>
       </c>
       <c r="G3" t="n">
-        <v>1.239</v>
+        <v>1.244</v>
       </c>
       <c r="H3" t="n">
         <v>1.194</v>
       </c>
       <c r="I3" t="n">
-        <v>0.778</v>
+        <v>0.806</v>
       </c>
       <c r="J3" t="n">
         <v>0.721</v>
       </c>
       <c r="K3" t="n">
-        <v>0.577</v>
+        <v>0.592</v>
       </c>
       <c r="L3" t="n">
         <v>0.46</v>
       </c>
       <c r="M3" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="4">
@@ -678,25 +678,25 @@
         <v>6.006</v>
       </c>
       <c r="G4" t="n">
-        <v>1.314</v>
+        <v>1.327</v>
       </c>
       <c r="H4" t="n">
         <v>1.267</v>
       </c>
       <c r="I4" t="n">
-        <v>0.863</v>
+        <v>0.828</v>
       </c>
       <c r="J4" t="n">
         <v>0.808</v>
       </c>
       <c r="K4" t="n">
-        <v>0.632</v>
+        <v>0.621</v>
       </c>
       <c r="L4" t="n">
         <v>0.334</v>
       </c>
       <c r="M4" t="n">
-        <v>0.438</v>
+        <v>0.443</v>
       </c>
     </row>
     <row r="5">
@@ -719,25 +719,25 @@
         <v>5.935</v>
       </c>
       <c r="G5" t="n">
-        <v>1.482</v>
+        <v>1.48</v>
       </c>
       <c r="H5" t="n">
         <v>0.785</v>
       </c>
       <c r="I5" t="n">
-        <v>0.923</v>
+        <v>0.921</v>
       </c>
       <c r="J5" t="n">
         <v>0.73</v>
       </c>
       <c r="K5" t="n">
-        <v>0.674</v>
+        <v>0.687</v>
       </c>
       <c r="L5" t="n">
         <v>0.418</v>
       </c>
       <c r="M5" t="n">
-        <v>0.469</v>
+        <v>0.479</v>
       </c>
     </row>
     <row r="6">
@@ -760,25 +760,25 @@
         <v>6.396</v>
       </c>
       <c r="G6" t="n">
-        <v>1.275</v>
+        <v>1.263</v>
       </c>
       <c r="H6" t="n">
         <v>1.442</v>
       </c>
       <c r="I6" t="n">
-        <v>0.818</v>
+        <v>0.824</v>
       </c>
       <c r="J6" t="n">
         <v>0.363</v>
       </c>
       <c r="K6" t="n">
-        <v>0.603</v>
+        <v>0.612</v>
       </c>
       <c r="L6" t="n">
         <v>0.346</v>
       </c>
       <c r="M6" t="n">
-        <v>0.422</v>
+        <v>0.439</v>
       </c>
     </row>
     <row r="7">
@@ -801,25 +801,25 @@
         <v>6.087</v>
       </c>
       <c r="G7" t="n">
-        <v>1.284</v>
+        <v>1.294</v>
       </c>
       <c r="H7" t="n">
         <v>1.02</v>
       </c>
       <c r="I7" t="n">
-        <v>0.825</v>
+        <v>0.829</v>
       </c>
       <c r="J7" t="n">
         <v>0.806</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6</v>
+        <v>0.596</v>
       </c>
       <c r="L7" t="n">
         <v>0.308</v>
       </c>
       <c r="M7" t="n">
-        <v>0.418</v>
+        <v>0.431</v>
       </c>
     </row>
   </sheetData>

--- a/Reproduce6 - AnalysisBySystem/Data_Analysis/generatedData/EFA_Summary_Consolidated.xlsx
+++ b/Reproduce6 - AnalysisBySystem/Data_Analysis/generatedData/EFA_Summary_Consolidated.xlsx
@@ -596,25 +596,25 @@
         <v>5.41</v>
       </c>
       <c r="G2" t="n">
-        <v>0.755</v>
+        <v>0.791</v>
       </c>
       <c r="H2" t="n">
         <v>0.888</v>
       </c>
       <c r="I2" t="n">
-        <v>0.363</v>
+        <v>0.38</v>
       </c>
       <c r="J2" t="n">
         <v>0.533</v>
       </c>
       <c r="K2" t="n">
-        <v>0.275</v>
+        <v>0.28</v>
       </c>
       <c r="L2" t="n">
         <v>0.283</v>
       </c>
       <c r="M2" t="n">
-        <v>0.201</v>
+        <v>0.204</v>
       </c>
     </row>
     <row r="3">
@@ -637,25 +637,25 @@
         <v>4.609</v>
       </c>
       <c r="G3" t="n">
-        <v>1.244</v>
+        <v>1.248</v>
       </c>
       <c r="H3" t="n">
         <v>1.194</v>
       </c>
       <c r="I3" t="n">
-        <v>0.806</v>
+        <v>0.799</v>
       </c>
       <c r="J3" t="n">
         <v>0.721</v>
       </c>
       <c r="K3" t="n">
-        <v>0.592</v>
+        <v>0.595</v>
       </c>
       <c r="L3" t="n">
         <v>0.46</v>
       </c>
       <c r="M3" t="n">
-        <v>0.41</v>
+        <v>0.424</v>
       </c>
     </row>
     <row r="4">
@@ -678,25 +678,25 @@
         <v>6.006</v>
       </c>
       <c r="G4" t="n">
-        <v>1.327</v>
+        <v>1.322</v>
       </c>
       <c r="H4" t="n">
         <v>1.267</v>
       </c>
       <c r="I4" t="n">
-        <v>0.828</v>
+        <v>0.831</v>
       </c>
       <c r="J4" t="n">
         <v>0.808</v>
       </c>
       <c r="K4" t="n">
-        <v>0.621</v>
+        <v>0.628</v>
       </c>
       <c r="L4" t="n">
         <v>0.334</v>
       </c>
       <c r="M4" t="n">
-        <v>0.443</v>
+        <v>0.441</v>
       </c>
     </row>
     <row r="5">
@@ -719,25 +719,25 @@
         <v>5.935</v>
       </c>
       <c r="G5" t="n">
-        <v>1.48</v>
+        <v>1.465</v>
       </c>
       <c r="H5" t="n">
         <v>0.785</v>
       </c>
       <c r="I5" t="n">
-        <v>0.921</v>
+        <v>0.936</v>
       </c>
       <c r="J5" t="n">
         <v>0.73</v>
       </c>
       <c r="K5" t="n">
-        <v>0.687</v>
+        <v>0.685</v>
       </c>
       <c r="L5" t="n">
         <v>0.418</v>
       </c>
       <c r="M5" t="n">
-        <v>0.479</v>
+        <v>0.465</v>
       </c>
     </row>
     <row r="6">
@@ -760,25 +760,25 @@
         <v>6.396</v>
       </c>
       <c r="G6" t="n">
-        <v>1.263</v>
+        <v>1.277</v>
       </c>
       <c r="H6" t="n">
         <v>1.442</v>
       </c>
       <c r="I6" t="n">
-        <v>0.824</v>
+        <v>0.825</v>
       </c>
       <c r="J6" t="n">
         <v>0.363</v>
       </c>
       <c r="K6" t="n">
-        <v>0.612</v>
+        <v>0.614</v>
       </c>
       <c r="L6" t="n">
         <v>0.346</v>
       </c>
       <c r="M6" t="n">
-        <v>0.439</v>
+        <v>0.432</v>
       </c>
     </row>
     <row r="7">
@@ -807,7 +807,7 @@
         <v>1.02</v>
       </c>
       <c r="I7" t="n">
-        <v>0.829</v>
+        <v>0.811</v>
       </c>
       <c r="J7" t="n">
         <v>0.806</v>
@@ -819,7 +819,7 @@
         <v>0.308</v>
       </c>
       <c r="M7" t="n">
-        <v>0.431</v>
+        <v>0.434</v>
       </c>
     </row>
   </sheetData>
